--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -1192,18 +1192,18 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Onex alquila ph en neptunia sur</t>
+          <t>Onex alquila ph en neptinia sur a metros de la playa</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa.  ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo)  ???? Garantías: ANDA, CGN o aseguradoras  ???? Comisión inmobiliaria: 1 mes + IVA  ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4485</t>
+          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa. APTO 3 ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo) ???? Garantías: ANDA, CGN o aseguradoras ???? Comisión inmobiliaria: 1 mes + IVA ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4571</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>193728253</t>
+          <t>193818874</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1212,7 +1212,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptunia-sur/193728253</t>
+          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptinia-sur-a-metros-de-la-playa/193818874</t>
         </is>
       </c>
     </row>
@@ -1231,18 +1231,18 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Onex alquila ph en neptinia sur a metros de la playa</t>
+          <t>Onex alquila ph en neptunia sur</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa. APTO 3 ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo) ???? Garantías: ANDA, CGN o aseguradoras ???? Comisión inmobiliaria: 1 mes + IVA ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4571</t>
+          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa.  ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo)  ???? Garantías: ANDA, CGN o aseguradoras  ???? Comisión inmobiliaria: 1 mes + IVA  ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4485</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>193818874</t>
+          <t>193728253</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1251,7 +1251,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptinia-sur-a-metros-de-la-playa/193818874</t>
+          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptunia-sur/193728253</t>
         </is>
       </c>
     </row>
@@ -1442,22 +1442,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>En alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>Preciosa casa de 1 dormitorio, en zona privilegiada, ideal persona sola o pareja  Cocina, living comedor.  Aire acondicionado. Baño con cabina de ducha.  Entrada compartida.  Patio independiente con parrillero individual para cada casa, con su division. Predio totalmente cercado con muro de 1 metro y medio.  Instalación para lavarropa, instalación para garrafa del lado de afuera. Se alquila sin muebles.  No se aceptan mascotas. En el precio esta incluido el wifi.   $17.500 Garantía unicamente de aseguradoras. Referencia Interna : Tera-2074</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194147141</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1466,7 +1466,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/en-alquiler-casa-de-1-dormitorio-en-neptunia/194147141</t>
         </is>
       </c>
     </row>
@@ -1485,22 +1485,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>En alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Preciosa casa de 1 dormitorio, en zona privilegiada, ideal persona sola o pareja  Cocina, living comedor.  Aire acondicionado. Baño con cabina de ducha.  Entrada compartida.  Patio independiente con parrillero individual para cada casa, con su division. Predio totalmente cercado con muro de 1 metro y medio.  Instalación para lavarropa, instalación para garrafa del lado de afuera. Se alquila sin muebles.  No se aceptan mascotas. En el precio esta incluido el wifi.   $17.500 Garantía unicamente de aseguradoras. Referencia Interna : Tera-2074</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194147141</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1509,7 +1509,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/en-alquiler-casa-de-1-dormitorio-en-neptunia/194147141</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -576,7 +576,7 @@
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -601,7 +601,7 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -1192,18 +1192,18 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Onex alquila ph en neptinia sur a metros de la playa</t>
+          <t>Onex alquila ph en neptunia sur</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa. APTO 3 ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo) ???? Garantías: ANDA, CGN o aseguradoras ???? Comisión inmobiliaria: 1 mes + IVA ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4571</t>
+          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa.  ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo)  ???? Garantías: ANDA, CGN o aseguradoras  ???? Comisión inmobiliaria: 1 mes + IVA  ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4485</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>193818874</t>
+          <t>193728253</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1212,7 +1212,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptinia-sur-a-metros-de-la-playa/193818874</t>
+          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptunia-sur/193728253</t>
         </is>
       </c>
     </row>
@@ -1231,18 +1231,18 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Onex alquila ph en neptunia sur</t>
+          <t>Onex alquila ph en neptinia sur a metros de la playa</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa.  ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo)  ???? Garantías: ANDA, CGN o aseguradoras  ???? Comisión inmobiliaria: 1 mes + IVA  ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4485</t>
+          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa. APTO 3 ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo) ???? Garantías: ANDA, CGN o aseguradoras ???? Comisión inmobiliaria: 1 mes + IVA ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4571</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>193728253</t>
+          <t>193818874</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1251,7 +1251,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptunia-sur/193728253</t>
+          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptinia-sur-a-metros-de-la-playa/193818874</t>
         </is>
       </c>
     </row>
@@ -1700,22 +1700,22 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I18" s="2" t="b">
@@ -1724,7 +1724,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1743,22 +1743,22 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I19" s="2" t="b">
@@ -1767,7 +1767,7 @@
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -501,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -526,7 +526,7 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -551,7 +551,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1000125" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -576,7 +576,7 @@
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -584,56 +584,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="752475" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -936,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1442,22 +1392,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>En alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Preciosa casa de 1 dormitorio, en zona privilegiada, ideal persona sola o pareja  Cocina, living comedor.  Aire acondicionado. Baño con cabina de ducha.  Entrada compartida.  Patio independiente con parrillero individual para cada casa, con su division. Predio totalmente cercado con muro de 1 metro y medio.  Instalación para lavarropa, instalación para garrafa del lado de afuera. Se alquila sin muebles.  No se aceptan mascotas. En el precio esta incluido el wifi.   $17.500 Garantía unicamente de aseguradoras. Referencia Interna : Tera-2074</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>194147141</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1466,7 +1416,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/en-alquiler-casa-de-1-dormitorio-en-neptunia/194147141</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1485,22 +1435,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1509,7 +1459,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1523,27 +1473,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1552,7 +1502,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1566,27 +1516,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
@@ -1595,7 +1545,7 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1609,27 +1559,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I16" s="2" t="b">
@@ -1638,7 +1588,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1652,27 +1602,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio amueblado en colonia nicolich</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Cno. de las Torcacitas esquina Cno. de los Pinos, a 300 mts de ruta 102  La unidad se encuentra completamente AMOBLADA  Cuenta con: Estar comedor Cocina integrada Un dormitorio con aire acondicionado Baño completo Derecho a estacionar un vehículo  ALQUILER: $15.500 GASTOS COMUNES: $500 GARANTIAS: LUC + MES DE DEPÓSITO POR MOBILIARIO.  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp O ***llamadas.   *Esta propiedad no admite mascotas.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>193917295</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I17" s="2" t="b">
@@ -1681,7 +1631,7 @@
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-amueblado-en-colonia-nicolich/193917295</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1695,27 +1645,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194241014</t>
         </is>
       </c>
       <c r="I18" s="2" t="b">
@@ -1724,98 +1674,12 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="110" customHeight="1">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>15.000</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>193878393</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="110" customHeight="1">
-      <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>13.500</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>194241014</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K20"/>
+  <autoFilter ref="A1:K18"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1834,10 +1698,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +31,10 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0027AE60"/>
     </font>
     <font>
       <color rgb="000563C1"/>
@@ -77,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,10 +89,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -176,7 +183,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1905000" cy="1162050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -226,7 +233,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +258,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1000125" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -301,7 +308,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1000125" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -326,7 +333,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -351,7 +358,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +383,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +408,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +433,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -476,7 +483,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -501,7 +508,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -526,7 +533,7 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -551,7 +558,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -559,31 +566,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -886,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -961,44 +943,42 @@
     </row>
     <row r="2" ht="110" customHeight="1">
       <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>UYU</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>21.000</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Casita a una cuadra del arroyo pando</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
+          <t>14.500</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler Casa 1dorm Los Aromos Nueva C/patio/ Alero/cochera A Metros De Cno Ventura  A Pocas Cuadras De Los Aromos Terreno Rodeado De Muros Se Acepta Seguros De Alquiler Maphre/sura/porto Xanda$17.400</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1 dorm. | 1 baño | 32 m² totales</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>193060994</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="b">
-        <v>0</v>
-      </c>
+          <t>32 m²</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.uy/MLU-698676579-alquiler-casa-1dorm-los-aromos-nueva-cpatio-alerocochera-a-metros-de-cno-ventura-a-pocas-cuadras-de-los-aromos-terreno-rodeado-de-muros-se-acepta-seguros-de-alquiler-maphresuraporto-xanda17400-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=cad099ca-b703-4a24-90c0-6eb724219ea3&amp;sid=search</t>
         </is>
       </c>
     </row>
@@ -1012,36 +992,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>21.000</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Casa en alquiler! 2 dormitorios colonia nicolich</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>ALQUILER! COLONIA NICOLICH A METROS DE RUTA 101 Y PROXIMA AL AEROPUERTO CASA AL FONDO Living comedor Cocina integrada 2 Dormitorios Baño completo Jardin al frente y fondo Lugar para auto GARNATIAS Anda, Contaduria o Porto Seguro</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>20.000</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Colonia-casa de campo el quinton</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>194107908</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-colonia-nicolich/194107908</t>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -1055,32 +1031,36 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Colonia-casa de campo el quinton</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>19.500</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -1094,36 +1074,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>19.000</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Onex alquila ph en neptunia sur</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa.  ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo)  ???? Garantías: ANDA, CGN o aseguradoras  ???? Comisión inmobiliaria: 1 mes + IVA  ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4485</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>193728253</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptunia-sur/193728253</t>
         </is>
       </c>
     </row>
@@ -1140,29 +1116,29 @@
           <t>19.000</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Onex alquila ph en neptunia sur</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa.  ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo)  ???? Garantías: ANDA, CGN o aseguradoras  ???? Comisión inmobiliaria: 1 mes + IVA  ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4485</t>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Onex alquila ph en neptinia sur a metros de la playa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa. APTO 3 ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo) ???? Garantías: ANDA, CGN o aseguradoras ???? Comisión inmobiliaria: 1 mes + IVA ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4571</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>193728253</t>
+          <t>193818874</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptunia-sur/193728253</t>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptinia-sur-a-metros-de-la-playa/193818874</t>
         </is>
       </c>
     </row>
@@ -1179,29 +1155,33 @@
           <t>19.000</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Onex alquila ph en neptinia sur a metros de la playa</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa. APTO 3 ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo) ???? Garantías: ANDA, CGN o aseguradoras ???? Comisión inmobiliaria: 1 mes + IVA ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4571</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>193818874</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptinia-sur-a-metros-de-la-playa/193818874</t>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1218,14 +1198,14 @@
           <t>19.000</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1235,16 +1215,16 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194228541</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
         </is>
       </c>
     </row>
@@ -1258,36 +1238,36 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
+          <t>18.500</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler&amp;nbsp; Casa de 1 dormitorio en Neptunia Sur, Canelones.&amp;nbsp;Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa.&amp;nbsp;Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada.&amp;nbsp;Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente.&amp;nbsp;Baño completo.&amp;nbsp;Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194228541</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1304,33 +1284,33 @@
           <t>18.500</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler&amp;nbsp; Casa de 1 dormitorio en Neptunia Sur, Canelones.&amp;nbsp;Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa.&amp;nbsp;Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada.&amp;nbsp;Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente.&amp;nbsp;Baño completo.&amp;nbsp;Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Descubra esta joya residencial: una casa íntima, como a estrenar, con amplio terreno y encanto inigualable.</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Descubra esta preciosa casa a estrenar, una joya totalmente independiente al frente, diseñada para ofrecerle la máxima privacidad y confort. Construida con un innovador sistema modular de excelente calidad, esta propiedad garantiza durabilidad y un diseño moderno.  Con un metraje interno de 40m² inteligentemente distribuidos y un generoso terreno propio de 300m², disfrutará de amplios espacios tanto interiores como exteriores. El luminoso living comedor con cocina integrada es el corazón del hogar, bañado por luz natural y equipado con aire acondicionado para su confort. La cocina, funcional y elegante, cuenta con muebles bajo y sobre mesada, además de un sistema de extracción, facilitando sus tareas culinarias.  La habitación principal es excepcionalmente amplia, diseñada para su descanso, con un módulo de ventana que incluye persiana para un control óptimo de la luz. El baño, un verdadero oasis de relajación, está totalmente equipado con una moderna ducha escocesa, bacha con mueble y mesada, instalación preparada para lavarropas, sistema de extracción y luz natural, combinando funcionalidad y estilo.  No pierda la oportunidad de conocer esta propiedad única que redefine el concepto de hogar. Consulte por opciones de garantías y prepárese para vivir la experiencia de estrenar su nuevo hogar.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194078366</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/descubra-esta-joya-residencial-una-casa-intima-como-a-estrenar-con-amplio-terreno-y-encanto-inigualable/194078366</t>
         </is>
       </c>
     </row>
@@ -1344,36 +1324,36 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18.500</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Descubra esta joya residencial: una casa íntima, como a estrenar, con amplio terreno y encanto inigualable.</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Descubra esta preciosa casa a estrenar, una joya totalmente independiente al frente, diseñada para ofrecerle la máxima privacidad y confort. Construida con un innovador sistema modular de excelente calidad, esta propiedad garantiza durabilidad y un diseño moderno.  Con un metraje interno de 40m² inteligentemente distribuidos y un generoso terreno propio de 300m², disfrutará de amplios espacios tanto interiores como exteriores. El luminoso living comedor con cocina integrada es el corazón del hogar, bañado por luz natural y equipado con aire acondicionado para su confort. La cocina, funcional y elegante, cuenta con muebles bajo y sobre mesada, además de un sistema de extracción, facilitando sus tareas culinarias.  La habitación principal es excepcionalmente amplia, diseñada para su descanso, con un módulo de ventana que incluye persiana para un control óptimo de la luz. El baño, un verdadero oasis de relajación, está totalmente equipado con una moderna ducha escocesa, bacha con mueble y mesada, instalación preparada para lavarropas, sistema de extracción y luz natural, combinando funcionalidad y estilo.  No pierda la oportunidad de conocer esta propiedad única que redefine el concepto de hogar. Consulte por opciones de garantías y prepárese para vivir la experiencia de estrenar su nuevo hogar.</t>
+          <t>17.500</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>194078366</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/descubra-esta-joya-residencial-una-casa-intima-como-a-estrenar-con-amplio-terreno-y-encanto-inigualable/194078366</t>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1390,33 +1370,33 @@
           <t>17.500</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1430,36 +1410,36 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>15.900</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1473,36 +1453,36 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>15.500</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1516,36 +1496,36 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>15.000</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1562,33 +1542,33 @@
           <t>15.000</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1602,84 +1582,41 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>13.500</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194241014</t>
         </is>
       </c>
       <c r="I17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="110" customHeight="1">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>13.500</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>194241014</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K18"/>
+  <autoFilter ref="A1:K17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1697,9 +1634,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,10 +31,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0027AE60"/>
     </font>
     <font>
       <color rgb="000563C1"/>
@@ -81,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -89,13 +85,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -183,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1162050"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -208,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -233,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1000125" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -283,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1000125" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -308,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -333,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -358,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -383,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -408,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -458,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -483,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -508,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -533,7 +526,7 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -541,31 +534,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -868,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -943,42 +911,40 @@
     </row>
     <row r="2" ht="110" customHeight="1">
       <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>UYU</t>
+          <t>$</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>14.500</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Alquiler Casa 1dorm Los Aromos Nueva C/patio/ Alero/cochera A Metros De Cno Ventura  A Pocas Cuadras De Los Aromos Terreno Rodeado De Muros Se Acepta Seguros De Alquiler Maphre/sura/porto Xanda$17.400</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1 dorm. | 1 baño | 32 m² totales</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>32 m²</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>20.000</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Colonia-casa de campo el quinton</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>194090773</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://casa.mercadolibre.com.uy/MLU-698676579-alquiler-casa-1dorm-los-aromos-nueva-cpatio-alerocochera-a-metros-de-cno-ventura-a-pocas-cuadras-de-los-aromos-terreno-rodeado-de-muros-se-acepta-seguros-de-alquiler-maphresuraporto-xanda17400-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=cad099ca-b703-4a24-90c0-6eb724219ea3&amp;sid=search</t>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -992,32 +958,36 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Colonia-casa de campo el quinton</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>19.500</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -1031,36 +1001,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>19.000</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Onex alquila ph en neptunia sur</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa.  ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo)  ???? Garantías: ANDA, CGN o aseguradoras  ???? Comisión inmobiliaria: 1 mes + IVA  ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4485</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>193728253</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptunia-sur/193728253</t>
         </is>
       </c>
     </row>
@@ -1077,29 +1043,29 @@
           <t>19.000</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Onex alquila ph en neptunia sur</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa.  ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo)  ???? Garantías: ANDA, CGN o aseguradoras  ???? Comisión inmobiliaria: 1 mes + IVA  ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4485</t>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Onex alquila ph en neptinia sur a metros de la playa</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa. APTO 3 ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo) ???? Garantías: ANDA, CGN o aseguradoras ???? Comisión inmobiliaria: 1 mes + IVA ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4571</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193728253</t>
+          <t>193818874</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptunia-sur/193728253</t>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptinia-sur-a-metros-de-la-playa/193818874</t>
         </is>
       </c>
     </row>
@@ -1116,29 +1082,33 @@
           <t>19.000</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Onex alquila ph en neptinia sur a metros de la playa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa. APTO 3 ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo) ???? Garantías: ANDA, CGN o aseguradoras ???? Comisión inmobiliaria: 1 mes + IVA ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4571</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>193818874</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptinia-sur-a-metros-de-la-playa/193818874</t>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1155,14 +1125,14 @@
           <t>19.000</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1172,16 +1142,16 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194228541</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
         </is>
       </c>
     </row>
@@ -1195,36 +1165,36 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
+          <t>18.500</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler&amp;nbsp; Casa de 1 dormitorio en Neptunia Sur, Canelones.&amp;nbsp;Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa.&amp;nbsp;Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada.&amp;nbsp;Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente.&amp;nbsp;Baño completo.&amp;nbsp;Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194228541</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1241,33 +1211,33 @@
           <t>18.500</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Alquiler&amp;nbsp; Casa de 1 dormitorio en Neptunia Sur, Canelones.&amp;nbsp;Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa.&amp;nbsp;Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada.&amp;nbsp;Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente.&amp;nbsp;Baño completo.&amp;nbsp;Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Descubra esta joya residencial: una casa íntima, como a estrenar, con amplio terreno y encanto inigualable.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Descubra esta preciosa casa a estrenar, una joya totalmente independiente al frente, diseñada para ofrecerle la máxima privacidad y confort. Construida con un innovador sistema modular de excelente calidad, esta propiedad garantiza durabilidad y un diseño moderno.  Con un metraje interno de 40m² inteligentemente distribuidos y un generoso terreno propio de 300m², disfrutará de amplios espacios tanto interiores como exteriores. El luminoso living comedor con cocina integrada es el corazón del hogar, bañado por luz natural y equipado con aire acondicionado para su confort. La cocina, funcional y elegante, cuenta con muebles bajo y sobre mesada, además de un sistema de extracción, facilitando sus tareas culinarias.  La habitación principal es excepcionalmente amplia, diseñada para su descanso, con un módulo de ventana que incluye persiana para un control óptimo de la luz. El baño, un verdadero oasis de relajación, está totalmente equipado con una moderna ducha escocesa, bacha con mueble y mesada, instalación preparada para lavarropas, sistema de extracción y luz natural, combinando funcionalidad y estilo.  No pierda la oportunidad de conocer esta propiedad única que redefine el concepto de hogar. Consulte por opciones de garantías y prepárese para vivir la experiencia de estrenar su nuevo hogar.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194078366</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/descubra-esta-joya-residencial-una-casa-intima-como-a-estrenar-con-amplio-terreno-y-encanto-inigualable/194078366</t>
         </is>
       </c>
     </row>
@@ -1281,36 +1251,36 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18.500</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Descubra esta joya residencial: una casa íntima, como a estrenar, con amplio terreno y encanto inigualable.</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Descubra esta preciosa casa a estrenar, una joya totalmente independiente al frente, diseñada para ofrecerle la máxima privacidad y confort. Construida con un innovador sistema modular de excelente calidad, esta propiedad garantiza durabilidad y un diseño moderno.  Con un metraje interno de 40m² inteligentemente distribuidos y un generoso terreno propio de 300m², disfrutará de amplios espacios tanto interiores como exteriores. El luminoso living comedor con cocina integrada es el corazón del hogar, bañado por luz natural y equipado con aire acondicionado para su confort. La cocina, funcional y elegante, cuenta con muebles bajo y sobre mesada, además de un sistema de extracción, facilitando sus tareas culinarias.  La habitación principal es excepcionalmente amplia, diseñada para su descanso, con un módulo de ventana que incluye persiana para un control óptimo de la luz. El baño, un verdadero oasis de relajación, está totalmente equipado con una moderna ducha escocesa, bacha con mueble y mesada, instalación preparada para lavarropas, sistema de extracción y luz natural, combinando funcionalidad y estilo.  No pierda la oportunidad de conocer esta propiedad única que redefine el concepto de hogar. Consulte por opciones de garantías y prepárese para vivir la experiencia de estrenar su nuevo hogar.</t>
+          <t>17.500</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>194078366</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/descubra-esta-joya-residencial-una-casa-intima-como-a-estrenar-con-amplio-terreno-y-encanto-inigualable/194078366</t>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1327,33 +1297,33 @@
           <t>17.500</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1367,36 +1337,36 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>15.900</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1410,36 +1380,36 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>15.500</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1453,36 +1423,36 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>15.000</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1499,33 +1469,33 @@
           <t>15.000</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1539,84 +1509,41 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>13.500</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194241014</t>
         </is>
       </c>
       <c r="I16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="110" customHeight="1">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>13.500</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>194241014</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K17"/>
+  <autoFilter ref="A1:K16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1633,9 +1560,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1000125" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1000125" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -919,23 +919,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>21.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Casita a una cuadra del arroyo pando</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193060994</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -944,7 +948,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
         </is>
       </c>
     </row>
@@ -958,27 +962,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>21.000</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Casa en alquiler! 2 dormitorios colonia nicolich</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+          <t>ALQUILER! COLONIA NICOLICH A METROS DE RUTA 101 Y PROXIMA AL AEROPUERTO CASA AL FONDO Living comedor Cocina integrada 2 Dormitorios Baño completo Jardin al frente y fondo Lugar para auto GARNATIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194107908</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -987,7 +991,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-colonia-nicolich/194107908</t>
         </is>
       </c>
     </row>
@@ -1001,23 +1005,23 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Onex alquila ph en neptunia sur</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa.  ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo)  ???? Garantías: ANDA, CGN o aseguradoras  ???? Comisión inmobiliaria: 1 mes + IVA  ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4485</t>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193728253</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1026,7 +1030,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptunia-sur/193728253</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -1040,23 +1044,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Onex alquila ph en neptinia sur a metros de la playa</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ????  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa. APTO 3 ✔️ 1 dormitorio ✔️ 1 baño ✔️ Cocina integrada ✔️ Living comedor ✔️ Entrada compartida  ???? Alquiler: $19.000 ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo) ???? Garantías: ANDA, CGN o aseguradoras ???? Comisión inmobiliaria: 1 mes + IVA ???? Consultá y coordiná tu visita con nuestros asesores Referencia Interna : Tera-4571</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193818874</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1065,7 +1073,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptinia-sur-a-metros-de-la-playa/193818874</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -326,109 +326,109 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1781175" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1019175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1019175"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1781175" cy="1333500"/>
-    <pic>
-      <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -534,6 +534,206 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1000125" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1000125" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1876425" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1323975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1000125" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -836,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1178,22 +1378,22 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Descubra esta joya residencial: una casa íntima, como a estrenar, con amplio terreno y encanto inigualable.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler&amp;nbsp; Casa de 1 dormitorio en Neptunia Sur, Canelones.&amp;nbsp;Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa.&amp;nbsp;Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada.&amp;nbsp;Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente.&amp;nbsp;Baño completo.&amp;nbsp;Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Descubra esta preciosa casa a estrenar, una joya totalmente independiente al frente, diseñada para ofrecerle la máxima privacidad y confort. Construida con un innovador sistema modular de excelente calidad, esta propiedad garantiza durabilidad y un diseño moderno.  Con un metraje interno de 40m² inteligentemente distribuidos y un generoso terreno propio de 300m², disfrutará de amplios espacios tanto interiores como exteriores. El luminoso living comedor con cocina integrada es el corazón del hogar, bañado por luz natural y equipado con aire acondicionado para su confort. La cocina, funcional y elegante, cuenta con muebles bajo y sobre mesada, además de un sistema de extracción, facilitando sus tareas culinarias.  La habitación principal es excepcionalmente amplia, diseñada para su descanso, con un módulo de ventana que incluye persiana para un control óptimo de la luz. El baño, un verdadero oasis de relajación, está totalmente equipado con una moderna ducha escocesa, bacha con mueble y mesada, instalación preparada para lavarropas, sistema de extracción y luz natural, combinando funcionalidad y estilo.  No pierda la oportunidad de conocer esta propiedad única que redefine el concepto de hogar. Consulte por opciones de garantías y prepárese para vivir la experiencia de estrenar su nuevo hogar.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194078366</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1202,7 +1402,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/descubra-esta-joya-residencial-una-casa-intima-como-a-estrenar-con-amplio-terreno-y-encanto-inigualable/194078366</t>
         </is>
       </c>
     </row>
@@ -1216,27 +1416,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18.500</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta joya residencial: una casa íntima, como a estrenar, con amplio terreno y encanto inigualable.</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta preciosa casa a estrenar, una joya totalmente independiente al frente, diseñada para ofrecerle la máxima privacidad y confort. Construida con un innovador sistema modular de excelente calidad, esta propiedad garantiza durabilidad y un diseño moderno.  Con un metraje interno de 40m² inteligentemente distribuidos y un generoso terreno propio de 300m², disfrutará de amplios espacios tanto interiores como exteriores. El luminoso living comedor con cocina integrada es el corazón del hogar, bañado por luz natural y equipado con aire acondicionado para su confort. La cocina, funcional y elegante, cuenta con muebles bajo y sobre mesada, además de un sistema de extracción, facilitando sus tareas culinarias.  La habitación principal es excepcionalmente amplia, diseñada para su descanso, con un módulo de ventana que incluye persiana para un control óptimo de la luz. El baño, un verdadero oasis de relajación, está totalmente equipado con una moderna ducha escocesa, bacha con mueble y mesada, instalación preparada para lavarropas, sistema de extracción y luz natural, combinando funcionalidad y estilo.  No pierda la oportunidad de conocer esta propiedad única que redefine el concepto de hogar. Consulte por opciones de garantías y prepárese para vivir la experiencia de estrenar su nuevo hogar.</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194078366</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1245,7 +1445,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/descubra-esta-joya-residencial-una-casa-intima-como-a-estrenar-con-amplio-terreno-y-encanto-inigualable/194078366</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1550,8 +1750,300 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="110" customHeight="1">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>UYU</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20.000</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler Casa Barros Blancos Con Cochera</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>1 dorm. | 1 baño | 60 m² totales</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>60 m²</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.uy/MLU-691652571-alquiler-casa-barros-blancos-con-cochera-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="110" customHeight="1">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>UYU</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19.500</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Amplia Casa De 2 Dormitorios En El Km 28 De Barros Blancos</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>2 dorm. | 1 baño | 100 m² totales</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100 m²</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.uy/MLU-700545203-amplia-casa-de-2-dormitorios-en-el-km-28-de-barros-blancos-_JM#polycard_client=search-desktop&amp;float_highlight=recent_publication&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="110" customHeight="1">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>UYU</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>17.900</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Casa De 1 Dormitorio En Neptunia Sur. Gran Terreno</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>1 dorm. | 1 baño | 488 m² totales</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>488 m²</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.uy/MLU-1498561944-casa-de-1-dormitorio-en-neptunia-sur-gran-terreno-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="110" customHeight="1">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>UYU</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>17.500</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler De Casa En Neptunia Sur, Primera Línea De Playa</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>1 dorm. | 1 baño | 60 m² totales</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>60 m²</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.uy/MLU-1488610256-alquiler-de-casa-en-neptunia-sur-primera-linea-de-playa-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="110" customHeight="1">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>UYU</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>17.500</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler De Casa De Dos Dormitorios, Ubicada En Una Zona Serena Y Tranquila, Con Estacionamiento Privado.</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>2 dorm. | 1 baño | 30 m² totales</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>30 m²</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.uy/MLU-1479592858-alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="110" customHeight="1">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>UYU</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>17.000</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Dos Dormitorios En Neptunia</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>2 dorm. | 1 baño</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.uy/MLU-1473714740-dos-dormitorios-en-neptunia-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="110" customHeight="1">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>UYU</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>13.500</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler Casa Un Dormitorio En Barros Blancos</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>1 dorm. | 1 baño | 82 m² totales</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>82 m²</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.uy/MLU-1501874064-alquiler-casa-un-dormitorio-en-barros-blancos-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=2&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="110" customHeight="1">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>UYU</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>12.900</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Casa Alquiler 1 Dormitorio Neptunia Sur</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>1 dorm. | 1 baño | 40 m² totales</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>40 m²</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>https://casa.mercadolibre.com.uy/MLU-696147373-casa-alquiler-1-dormitorio-neptunia-sur-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1568,8 +2060,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,256 +484,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1628775" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1000125" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1000125" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1876425" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1333500" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1323975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1000125" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1076325"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1036,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1119,27 +869,23 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>21.000</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Casita a una cuadra del arroyo pando</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>193060994</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -1148,7 +894,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -1162,27 +908,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>21.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler! 2 dormitorios colonia nicolich</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>ALQUILER! COLONIA NICOLICH A METROS DE RUTA 101 Y PROXIMA AL AEROPUERTO CASA AL FONDO Living comedor Cocina integrada 2 Dormitorios Baño completo Jardin al frente y fondo Lugar para auto GARNATIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>194107908</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -1191,7 +937,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-colonia-nicolich/194107908</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -1205,23 +951,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1230,7 +980,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1244,27 +994,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194228541</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1273,7 +1023,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
         </is>
       </c>
     </row>
@@ -1287,27 +1037,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>18.500</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Descubra esta joya residencial: una casa íntima, como a estrenar, con amplio terreno y encanto inigualable.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Descubra esta preciosa casa a estrenar, una joya totalmente independiente al frente, diseñada para ofrecerle la máxima privacidad y confort. Construida con un innovador sistema modular de excelente calidad, esta propiedad garantiza durabilidad y un diseño moderno.  Con un metraje interno de 40m² inteligentemente distribuidos y un generoso terreno propio de 300m², disfrutará de amplios espacios tanto interiores como exteriores. El luminoso living comedor con cocina integrada es el corazón del hogar, bañado por luz natural y equipado con aire acondicionado para su confort. La cocina, funcional y elegante, cuenta con muebles bajo y sobre mesada, además de un sistema de extracción, facilitando sus tareas culinarias.  La habitación principal es excepcionalmente amplia, diseñada para su descanso, con un módulo de ventana que incluye persiana para un control óptimo de la luz. El baño, un verdadero oasis de relajación, está totalmente equipado con una moderna ducha escocesa, bacha con mueble y mesada, instalación preparada para lavarropas, sistema de extracción y luz natural, combinando funcionalidad y estilo.  No pierda la oportunidad de conocer esta propiedad única que redefine el concepto de hogar. Consulte por opciones de garantías y prepárese para vivir la experiencia de estrenar su nuevo hogar.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194078366</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1316,7 +1066,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/descubra-esta-joya-residencial-una-casa-intima-como-a-estrenar-con-amplio-terreno-y-encanto-inigualable/194078366</t>
         </is>
       </c>
     </row>
@@ -1330,27 +1080,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194228541</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1359,7 +1109,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1373,27 +1123,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18.500</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta joya residencial: una casa íntima, como a estrenar, con amplio terreno y encanto inigualable.</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta preciosa casa a estrenar, una joya totalmente independiente al frente, diseñada para ofrecerle la máxima privacidad y confort. Construida con un innovador sistema modular de excelente calidad, esta propiedad garantiza durabilidad y un diseño moderno.  Con un metraje interno de 40m² inteligentemente distribuidos y un generoso terreno propio de 300m², disfrutará de amplios espacios tanto interiores como exteriores. El luminoso living comedor con cocina integrada es el corazón del hogar, bañado por luz natural y equipado con aire acondicionado para su confort. La cocina, funcional y elegante, cuenta con muebles bajo y sobre mesada, además de un sistema de extracción, facilitando sus tareas culinarias.  La habitación principal es excepcionalmente amplia, diseñada para su descanso, con un módulo de ventana que incluye persiana para un control óptimo de la luz. El baño, un verdadero oasis de relajación, está totalmente equipado con una moderna ducha escocesa, bacha con mueble y mesada, instalación preparada para lavarropas, sistema de extracción y luz natural, combinando funcionalidad y estilo.  No pierda la oportunidad de conocer esta propiedad única que redefine el concepto de hogar. Consulte por opciones de garantías y prepárese para vivir la experiencia de estrenar su nuevo hogar.</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194078366</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1402,7 +1152,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/descubra-esta-joya-residencial-una-casa-intima-como-a-estrenar-con-amplio-terreno-y-encanto-inigualable/194078366</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1416,27 +1166,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1445,7 +1195,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1459,27 +1209,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1488,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1502,17 +1252,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1522,7 +1272,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1531,7 +1281,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1545,27 +1295,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1574,7 +1324,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1588,27 +1338,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1617,7 +1367,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1631,27 +1381,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194241014</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1660,390 +1410,12 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="110" customHeight="1">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>15.000</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>193627120</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="110" customHeight="1">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>13.500</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>194241014</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="110" customHeight="1">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>UYU</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>20.000</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler Casa Barros Blancos Con Cochera</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>1 dorm. | 1 baño | 60 m² totales</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>60 m²</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>https://casa.mercadolibre.com.uy/MLU-691652571-alquiler-casa-barros-blancos-con-cochera-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="110" customHeight="1">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>UYU</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>19.500</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Amplia Casa De 2 Dormitorios En El Km 28 De Barros Blancos</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>2 dorm. | 1 baño | 100 m² totales</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100 m²</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>https://casa.mercadolibre.com.uy/MLU-700545203-amplia-casa-de-2-dormitorios-en-el-km-28-de-barros-blancos-_JM#polycard_client=search-desktop&amp;float_highlight=recent_publication&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="110" customHeight="1">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>UYU</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>17.900</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Casa De 1 Dormitorio En Neptunia Sur. Gran Terreno</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>1 dorm. | 1 baño | 488 m² totales</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>488 m²</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>https://casa.mercadolibre.com.uy/MLU-1498561944-casa-de-1-dormitorio-en-neptunia-sur-gran-terreno-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="110" customHeight="1">
-      <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>UYU</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>17.500</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler De Casa En Neptunia Sur, Primera Línea De Playa</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>1 dorm. | 1 baño | 60 m² totales</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>60 m²</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>https://casa.mercadolibre.com.uy/MLU-1488610256-alquiler-de-casa-en-neptunia-sur-primera-linea-de-playa-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="110" customHeight="1">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>UYU</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>17.500</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler De Casa De Dos Dormitorios, Ubicada En Una Zona Serena Y Tranquila, Con Estacionamiento Privado.</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>2 dorm. | 1 baño | 30 m² totales</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>30 m²</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>https://casa.mercadolibre.com.uy/MLU-1479592858-alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="110" customHeight="1">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>UYU</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>17.000</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Dos Dormitorios En Neptunia</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>2 dorm. | 1 baño</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>https://casa.mercadolibre.com.uy/MLU-1473714740-dos-dormitorios-en-neptunia-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="110" customHeight="1">
-      <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>UYU</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>13.500</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler Casa Un Dormitorio En Barros Blancos</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>1 dorm. | 1 baño | 82 m² totales</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>82 m²</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>https://casa.mercadolibre.com.uy/MLU-1501874064-alquiler-casa-un-dormitorio-en-barros-blancos-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=2&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="110" customHeight="1">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>UYU</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>12.900</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Casa Alquiler 1 Dormitorio Neptunia Sur</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>1 dorm. | 1 baño | 40 m² totales</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>40 m²</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>https://casa.mercadolibre.com.uy/MLU-696147373-casa-alquiler-1-dormitorio-neptunia-sur-_JM#polycard_client=search-desktop&amp;price_drop=not_apply&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=d04e1eec-2c07-4bcb-9ddf-1923124887f0&amp;sid=search</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K24"/>
+  <autoFilter ref="A1:K14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -2058,18 +1430,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,6 +484,56 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="752475" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -786,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -869,23 +919,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>21.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Casita a una cuadra del arroyo pando</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193060994</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -894,7 +948,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
         </is>
       </c>
     </row>
@@ -908,27 +962,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>21.000</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Casa en alquiler! 2 dormitorios colonia nicolich</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+          <t>ALQUILER! COLONIA NICOLICH A METROS DE RUTA 101 Y PROXIMA AL AEROPUERTO CASA AL FONDO Living comedor Cocina integrada 2 Dormitorios Baño completo Jardin al frente y fondo Lugar para auto GARNATIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194107908</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -937,7 +991,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-colonia-nicolich/194107908</t>
         </is>
       </c>
     </row>
@@ -951,27 +1005,23 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -980,7 +1030,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -994,27 +1044,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>194228541</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1023,7 +1073,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -1037,27 +1087,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18.500</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta joya residencial: una casa íntima, como a estrenar, con amplio terreno y encanto inigualable.</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta preciosa casa a estrenar, una joya totalmente independiente al frente, diseñada para ofrecerle la máxima privacidad y confort. Construida con un innovador sistema modular de excelente calidad, esta propiedad garantiza durabilidad y un diseño moderno.  Con un metraje interno de 40m² inteligentemente distribuidos y un generoso terreno propio de 300m², disfrutará de amplios espacios tanto interiores como exteriores. El luminoso living comedor con cocina integrada es el corazón del hogar, bañado por luz natural y equipado con aire acondicionado para su confort. La cocina, funcional y elegante, cuenta con muebles bajo y sobre mesada, además de un sistema de extracción, facilitando sus tareas culinarias.  La habitación principal es excepcionalmente amplia, diseñada para su descanso, con un módulo de ventana que incluye persiana para un control óptimo de la luz. El baño, un verdadero oasis de relajación, está totalmente equipado con una moderna ducha escocesa, bacha con mueble y mesada, instalación preparada para lavarropas, sistema de extracción y luz natural, combinando funcionalidad y estilo.  No pierda la oportunidad de conocer esta propiedad única que redefine el concepto de hogar. Consulte por opciones de garantías y prepárese para vivir la experiencia de estrenar su nuevo hogar.</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194078366</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1066,7 +1116,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/descubra-esta-joya-residencial-una-casa-intima-como-a-estrenar-con-amplio-terreno-y-encanto-inigualable/194078366</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1080,27 +1130,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194228541</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1109,7 +1159,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
         </is>
       </c>
     </row>
@@ -1123,27 +1173,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>18.500</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Descubra esta joya residencial: una casa íntima, como a estrenar, con amplio terreno y encanto inigualable.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>Descubra esta preciosa casa a estrenar, una joya totalmente independiente al frente, diseñada para ofrecerle la máxima privacidad y confort. Construida con un innovador sistema modular de excelente calidad, esta propiedad garantiza durabilidad y un diseño moderno.  Con un metraje interno de 40m² inteligentemente distribuidos y un generoso terreno propio de 300m², disfrutará de amplios espacios tanto interiores como exteriores. El luminoso living comedor con cocina integrada es el corazón del hogar, bañado por luz natural y equipado con aire acondicionado para su confort. La cocina, funcional y elegante, cuenta con muebles bajo y sobre mesada, además de un sistema de extracción, facilitando sus tareas culinarias.  La habitación principal es excepcionalmente amplia, diseñada para su descanso, con un módulo de ventana que incluye persiana para un control óptimo de la luz. El baño, un verdadero oasis de relajación, está totalmente equipado con una moderna ducha escocesa, bacha con mueble y mesada, instalación preparada para lavarropas, sistema de extracción y luz natural, combinando funcionalidad y estilo.  No pierda la oportunidad de conocer esta propiedad única que redefine el concepto de hogar. Consulte por opciones de garantías y prepárese para vivir la experiencia de estrenar su nuevo hogar.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194078366</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1152,7 +1202,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/descubra-esta-joya-residencial-una-casa-intima-como-a-estrenar-con-amplio-terreno-y-encanto-inigualable/194078366</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1216,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1195,7 +1245,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1209,27 +1259,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1238,7 +1288,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1252,17 +1302,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1272,7 +1322,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1281,7 +1331,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1295,27 +1345,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1324,7 +1374,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1338,27 +1388,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1367,7 +1417,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1381,27 +1431,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194241014</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1410,12 +1460,98 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15.000</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>193878393</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13.500</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>194241014</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1430,8 +1566,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -501,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -1436,22 +1436,22 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1460,7 +1460,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1479,22 +1479,22 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
@@ -1503,7 +1503,7 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -501,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -509,31 +509,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -836,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1173,27 +1148,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18.500</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta joya residencial: una casa íntima, como a estrenar, con amplio terreno y encanto inigualable.</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta preciosa casa a estrenar, una joya totalmente independiente al frente, diseñada para ofrecerle la máxima privacidad y confort. Construida con un innovador sistema modular de excelente calidad, esta propiedad garantiza durabilidad y un diseño moderno.  Con un metraje interno de 40m² inteligentemente distribuidos y un generoso terreno propio de 300m², disfrutará de amplios espacios tanto interiores como exteriores. El luminoso living comedor con cocina integrada es el corazón del hogar, bañado por luz natural y equipado con aire acondicionado para su confort. La cocina, funcional y elegante, cuenta con muebles bajo y sobre mesada, además de un sistema de extracción, facilitando sus tareas culinarias.  La habitación principal es excepcionalmente amplia, diseñada para su descanso, con un módulo de ventana que incluye persiana para un control óptimo de la luz. El baño, un verdadero oasis de relajación, está totalmente equipado con una moderna ducha escocesa, bacha con mueble y mesada, instalación preparada para lavarropas, sistema de extracción y luz natural, combinando funcionalidad y estilo.  No pierda la oportunidad de conocer esta propiedad única que redefine el concepto de hogar. Consulte por opciones de garantías y prepárese para vivir la experiencia de estrenar su nuevo hogar.</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194078366</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1202,7 +1177,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/descubra-esta-joya-residencial-una-casa-intima-como-a-estrenar-con-amplio-terreno-y-encanto-inigualable/194078366</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1216,27 +1191,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1245,7 +1220,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1264,22 +1239,22 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1288,7 +1263,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1302,27 +1277,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1331,7 +1306,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1345,27 +1320,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1374,7 +1349,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1388,27 +1363,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1417,7 +1392,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1436,22 +1411,22 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1460,7 +1435,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1474,27 +1449,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194241014</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
@@ -1503,55 +1478,12 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="110" customHeight="1">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>13.500</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>194241014</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1567,9 +1499,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1885950" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -501,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -509,6 +509,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -811,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1368,22 +1393,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1392,7 +1417,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1411,22 +1436,22 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1435,7 +1460,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1449,27 +1474,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>14.000</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>194241014</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
@@ -1478,12 +1503,55 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13.500</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>194241014</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1499,8 +1567,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1885950" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -1393,22 +1393,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1417,7 +1417,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1436,22 +1436,22 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1460,7 +1460,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -962,27 +962,23 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>21.000</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler! 2 dormitorios colonia nicolich</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>ALQUILER! COLONIA NICOLICH A METROS DE RUTA 101 Y PROXIMA AL AEROPUERTO CASA AL FONDO Living comedor Cocina integrada 2 Dormitorios Baño completo Jardin al frente y fondo Lugar para auto GARNATIAS Anda, Contaduria o Porto Seguro</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>194107908</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -991,7 +987,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-colonia-nicolich/194107908</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -1005,23 +1001,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1030,7 +1030,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -1044,27 +1044,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1073,7 +1073,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194228541</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1116,7 +1116,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
         </is>
       </c>
     </row>
@@ -1130,27 +1130,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194228541</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1159,7 +1159,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1173,27 +1173,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1202,7 +1202,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1221,22 +1221,22 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1245,7 +1245,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1259,27 +1259,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1288,7 +1288,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1302,27 +1302,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1331,7 +1331,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1345,27 +1345,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1374,7 +1374,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1393,22 +1393,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1417,7 +1417,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1436,22 +1436,22 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1460,7 +1460,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -1350,22 +1350,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1374,7 +1374,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1417,7 +1417,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1436,22 +1436,22 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1460,7 +1460,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -501,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -509,31 +509,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -836,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -919,27 +894,23 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>21.000</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Casita a una cuadra del arroyo pando</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>193060994</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -948,7 +919,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -962,23 +933,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -987,7 +962,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -1001,27 +976,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1030,7 +1005,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1029,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1064,7 +1039,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194228541</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1073,7 +1048,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
         </is>
       </c>
     </row>
@@ -1087,27 +1062,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194228541</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1116,7 +1091,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1130,27 +1105,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1159,7 +1134,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1178,22 +1153,22 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1202,7 +1177,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1216,27 +1191,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1245,7 +1220,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1259,27 +1234,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1288,7 +1263,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1302,27 +1277,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1331,7 +1306,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1368,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1408,7 +1383,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1417,7 +1392,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1431,27 +1406,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>14.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1460,7 +1435,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
@@ -1474,27 +1449,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>194241014</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
@@ -1503,55 +1478,12 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="110" customHeight="1">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>13.500</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>194241014</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1567,9 +1499,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -501,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -509,6 +509,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -811,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -894,23 +919,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>21.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Casita a una cuadra del arroyo pando</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193060994</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -919,7 +948,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
         </is>
       </c>
     </row>
@@ -933,27 +962,23 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -962,7 +987,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -976,27 +1001,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1005,7 +1030,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1054,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1039,7 +1064,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>194228541</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1048,7 +1073,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1062,27 +1087,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194228541</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1091,7 +1116,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
         </is>
       </c>
     </row>
@@ -1105,27 +1130,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1134,7 +1159,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1153,22 +1178,22 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1177,7 +1202,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1191,27 +1216,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1220,7 +1245,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1234,27 +1259,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1263,7 +1288,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1302,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1306,7 +1331,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1393,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1383,7 +1408,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1392,7 +1417,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1406,27 +1431,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14.000</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1435,7 +1460,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1449,27 +1474,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>14.000</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>194241014</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
@@ -1478,12 +1503,55 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13.500</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>194241014</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1499,8 +1567,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -501,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -509,31 +509,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -836,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -919,27 +894,23 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>21.000</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Casita a una cuadra del arroyo pando</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>193060994</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -948,7 +919,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -962,23 +933,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -987,7 +962,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -1001,27 +976,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1030,7 +1005,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1029,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1064,7 +1039,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194228541</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1073,7 +1048,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
         </is>
       </c>
     </row>
@@ -1087,27 +1062,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194228541</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1116,7 +1091,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1130,27 +1105,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1159,7 +1134,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1178,22 +1153,22 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1202,7 +1177,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1216,27 +1191,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1245,7 +1220,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1259,27 +1234,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1288,7 +1263,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1302,27 +1277,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1331,7 +1306,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1350,22 +1325,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1374,7 +1349,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1368,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1408,7 +1383,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1417,7 +1392,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1431,27 +1406,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>14.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1460,7 +1435,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
@@ -1474,27 +1449,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>194241014</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
@@ -1503,55 +1478,12 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="110" customHeight="1">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>13.500</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>194241014</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1567,9 +1499,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,31 +484,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -811,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1019,27 +994,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Victoria Rodríguez MuñozLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Victoria Rodriguez Muñoz</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>194228541</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1048,7 +1023,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194228541</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1062,27 +1037,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1091,7 +1066,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1110,22 +1085,22 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1134,7 +1109,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1148,27 +1123,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1177,7 +1152,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1191,27 +1166,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1220,7 +1195,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1234,27 +1209,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1263,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1282,22 +1257,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1306,7 +1281,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1300,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1349,7 +1324,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1363,27 +1338,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>14.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1392,7 +1367,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
@@ -1406,27 +1381,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>194241014</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1435,55 +1410,12 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="110" customHeight="1">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>13.500</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>194241014</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1498,9 +1430,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -1214,22 +1214,22 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1238,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1324,7 +1324,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1214,22 +1214,22 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1238,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1257,22 +1257,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1281,7 +1281,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,6 +484,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -786,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -869,23 +894,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>21.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Casita a una cuadra del arroyo pando</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193060994</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -894,7 +923,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
         </is>
       </c>
     </row>
@@ -908,27 +937,23 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -937,7 +962,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -951,27 +976,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -980,7 +1005,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -994,27 +1019,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1023,7 +1048,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1037,27 +1062,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1066,7 +1091,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1085,22 +1110,22 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1109,7 +1134,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1123,27 +1148,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1152,7 +1177,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1191,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1195,7 +1220,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1209,27 +1234,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1238,7 +1263,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1257,22 +1282,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1281,7 +1306,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1325,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1324,7 +1349,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1338,27 +1363,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14.000</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1367,7 +1392,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1381,27 +1406,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>14.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194241014</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1410,12 +1435,55 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13.500</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>194241014</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1430,8 +1498,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -1325,22 +1325,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1349,7 +1349,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1368,22 +1368,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1392,7 +1392,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -501,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -509,6 +509,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -811,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1062,27 +1087,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Sofía DamianiLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Sofía Damiani</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194334606</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1091,7 +1116,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194334606</t>
         </is>
       </c>
     </row>
@@ -1105,27 +1130,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1134,7 +1159,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1148,27 +1173,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1177,7 +1202,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1191,27 +1216,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1220,7 +1245,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1234,27 +1259,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1263,7 +1288,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1302,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1306,7 +1331,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1350,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1340,7 +1365,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1349,7 +1374,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1368,22 +1393,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1392,7 +1417,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1406,27 +1431,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14.000</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1435,7 +1460,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1449,27 +1474,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>14.000</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>194241014</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
@@ -1478,12 +1503,55 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13.500</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>194241014</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1499,8 +1567,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1374,7 +1374,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1393,22 +1393,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1417,7 +1417,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1436,22 +1436,22 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1460,7 +1460,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,56 +484,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="752475" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -836,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -919,27 +869,23 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>21.000</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Casita a una cuadra del arroyo pando</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>193060994</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -948,7 +894,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -962,23 +908,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -987,7 +937,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -1001,27 +951,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1030,7 +980,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1044,27 +994,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1073,7 +1023,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1087,27 +1037,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso. Contacto: Sofía DamianiLa propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101. Características de la propiedad:- Superficie total: 45 m² (cubiertos)- Ambientes: 1 dormitorio, 1 baño- Cochera: descubierta- Gastos comunes: UY$1.500- Servicios: agua corriente, calefón, campana de extracción en cocina- Orientación: norte- Antigüedad: 5 años- Garantías aceptadas: aseguradoras y anda- Contrato: 2 años, acepta mascota pequeñaLa propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya!Sofía Damiani</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194334606</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1116,7 +1066,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194334606</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1130,27 +1080,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1159,7 +1109,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1173,27 +1123,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1202,7 +1152,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1216,17 +1166,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1236,7 +1186,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1245,7 +1195,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1259,27 +1209,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1288,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1302,27 +1252,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1331,7 +1281,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1300,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1365,7 +1315,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1374,7 +1324,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1388,27 +1338,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>14.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1417,7 +1367,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
@@ -1431,27 +1381,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>194241014</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1460,98 +1410,12 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="110" customHeight="1">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>14.000</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>194293172</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="110" customHeight="1">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>13.500</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>194241014</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1566,10 +1430,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -1214,12 +1214,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1238,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1324,7 +1324,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1214,22 +1214,22 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1238,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1257,22 +1257,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1281,7 +1281,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,6 +484,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -786,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -869,23 +894,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>21.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Casita a una cuadra del arroyo pando</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193060994</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -894,7 +923,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
         </is>
       </c>
     </row>
@@ -908,27 +937,23 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -937,7 +962,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -951,27 +976,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -980,7 +1005,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -994,27 +1019,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1023,7 +1048,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1037,27 +1062,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1066,7 +1091,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1080,27 +1105,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1109,7 +1134,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1123,27 +1148,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1152,7 +1177,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1191,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1195,7 +1220,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1209,27 +1234,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1238,7 +1263,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1257,22 +1282,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1281,7 +1306,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1325,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1315,7 +1340,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1324,7 +1349,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1338,27 +1363,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14.000</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1367,7 +1392,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1381,27 +1406,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>14.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194241014</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1410,12 +1435,55 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13.500</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>194241014</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1430,8 +1498,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,31 +484,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -811,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -894,27 +869,23 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>21.000</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Casita a una cuadra del arroyo pando</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>193060994</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -923,7 +894,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -937,23 +908,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -962,7 +937,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -976,27 +951,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1005,7 +980,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1019,27 +994,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1048,7 +1023,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1062,27 +1037,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1091,7 +1066,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1105,27 +1080,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1134,7 +1109,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1148,27 +1123,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1177,7 +1152,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1191,27 +1166,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1220,7 +1195,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1234,27 +1209,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1263,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1282,22 +1257,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1306,7 +1281,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1300,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1349,7 +1324,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1363,27 +1338,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>14.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1392,7 +1367,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
@@ -1406,27 +1381,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>194241014</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1435,55 +1410,12 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="110" customHeight="1">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>13.500</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>194241014</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1498,9 +1430,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -1214,22 +1214,22 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1238,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1281,7 +1281,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1324,7 +1324,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1214,22 +1214,22 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1238,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1257,22 +1257,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1281,7 +1281,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,6 +484,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -786,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -869,23 +894,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>21.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Casita a una cuadra del arroyo pando</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193060994</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -894,7 +923,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
         </is>
       </c>
     </row>
@@ -908,27 +937,23 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -937,7 +962,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -951,27 +976,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -980,7 +1005,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -994,27 +1019,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1023,7 +1048,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1037,27 +1062,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1066,7 +1091,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1080,27 +1105,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1109,7 +1134,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1123,27 +1148,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1152,7 +1177,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1191,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1195,7 +1220,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1209,27 +1234,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1238,7 +1263,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1257,22 +1282,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1281,7 +1306,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1325,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1315,7 +1340,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1324,7 +1349,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1338,27 +1363,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14.000</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1367,7 +1392,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1381,27 +1406,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>14.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194241014</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1410,12 +1435,55 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13.500</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>194241014</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1430,8 +1498,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,31 +484,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -811,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -894,27 +869,23 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>21.000</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Casita a una cuadra del arroyo pando</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>193060994</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -923,7 +894,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -937,23 +908,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -962,7 +937,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -976,27 +951,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1005,7 +980,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1019,27 +994,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1048,7 +1023,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1062,27 +1037,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1091,7 +1066,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1105,27 +1080,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1134,7 +1109,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1148,27 +1123,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1177,7 +1152,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1191,27 +1166,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1220,7 +1195,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1234,27 +1209,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1263,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1257,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1297,7 +1272,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1306,7 +1281,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1300,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1349,7 +1324,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1363,27 +1338,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>14.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1392,7 +1367,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
@@ -1406,27 +1381,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>194241014</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1435,55 +1410,12 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="110" customHeight="1">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>13.500</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>194241014</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1498,9 +1430,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,6 +484,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -786,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -869,23 +894,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>21.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Casita a una cuadra del arroyo pando</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193060994</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -894,7 +923,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
         </is>
       </c>
     </row>
@@ -908,27 +937,23 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -937,7 +962,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -951,27 +976,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -980,7 +1005,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -994,27 +1019,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1023,7 +1048,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1037,27 +1062,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1066,7 +1091,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1080,27 +1105,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1109,7 +1134,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1123,27 +1148,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1152,7 +1177,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1191,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1195,7 +1220,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1209,27 +1234,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1238,7 +1263,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1282,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1272,7 +1297,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1281,7 +1306,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1325,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1324,7 +1349,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1338,27 +1363,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14.000</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1367,7 +1392,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1381,27 +1406,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>14.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194241014</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1410,12 +1435,55 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13.500</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>194241014</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1430,8 +1498,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,31 +484,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -811,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -894,27 +869,23 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>21.000</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Casita a una cuadra del arroyo pando</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>193060994</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -923,7 +894,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -937,23 +908,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -962,7 +937,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -976,27 +951,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1005,7 +980,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1019,27 +994,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1048,7 +1023,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1062,27 +1037,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1091,7 +1066,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1105,27 +1080,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1134,7 +1109,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1148,27 +1123,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1177,7 +1152,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1191,27 +1166,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1220,7 +1195,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1234,27 +1209,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1263,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1257,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1297,7 +1272,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1306,7 +1281,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1300,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1349,7 +1324,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1363,27 +1338,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>14.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1392,7 +1367,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
@@ -1406,27 +1381,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>194387339</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1435,55 +1410,12 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="110" customHeight="1">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>13.500</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>194241014</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194241014</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1498,9 +1430,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -1338,27 +1338,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $14.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>194387339</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1367,7 +1367,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
@@ -1381,27 +1381,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>12.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194387339</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1410,7 +1410,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1019175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -484,6 +484,56 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="752475" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -786,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -869,23 +919,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>21.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Casita a una cuadra del arroyo pando</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193060994</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -894,7 +948,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
         </is>
       </c>
     </row>
@@ -908,27 +962,23 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -937,7 +987,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -951,27 +1001,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -980,7 +1030,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -994,27 +1044,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194405738</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1023,7 +1073,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
         </is>
       </c>
     </row>
@@ -1037,27 +1087,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1066,7 +1116,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1080,27 +1130,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1109,7 +1159,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1123,27 +1173,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>17.500</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194097290</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1152,7 +1202,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
         </is>
       </c>
     </row>
@@ -1166,17 +1216,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1186,7 +1236,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1195,7 +1245,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1209,27 +1259,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1238,7 +1288,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1252,27 +1302,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1281,7 +1331,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1350,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1324,7 +1374,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1338,27 +1388,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194387339</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1367,7 +1417,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1381,27 +1431,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12.000</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1410,12 +1460,98 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13.500</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>194387339</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12.000</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>194293172</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1430,8 +1566,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1019175"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -484,56 +484,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="752475" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -836,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -919,27 +869,23 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>21.000</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Casita a una cuadra del arroyo pando</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>193060994</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -948,7 +894,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -962,23 +908,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -987,7 +937,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -1001,27 +951,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194405738</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1030,7 +980,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1004,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1064,7 +1014,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>194405738</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1073,7 +1023,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1087,27 +1037,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1116,7 +1066,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1130,27 +1080,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1159,7 +1109,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1173,27 +1123,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler de casa de dos dormitorios, ubicada en una zona serena y tranquila, con estacionamiento privado.</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Descubra la tranquilidad y el confort en esta encantadora casa contenedor, lista para habitar. Con dos dormitorios acogedores y equipada con aire acondicionado para su máximo confort, esta propiedad ofrece un baño completo y una cocina funcional con campana extractora. La casa, de 30 m², se complementa con un ingenioso sobretecho que amplía el espacio a un total semiabierto de 60 m², ideal para disfrutar de una barbacoa con parrillero y un conveniente lugar para estacionamiento. Todo esto se enmarca en un extenso jardín privado de 900 m², delimitado vegetación natural, creando un oasis de serenidad. Los gastos comunes incluyen el servicio de agua y el mantenimiento del césped, garantizando una vida sin preocupaciones. Ubicada en una zona excepcionalmente tranquila, esta propiedad le brinda el privilegio de acceder libremente a las 2 hectáreas que conforman toda la finca, invitándole a disfrutar de la naturaleza y la paz que siempre ha deseado.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194097290</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1202,7 +1152,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-de-casa-de-dos-dormitorios-ubicada-en-una-zona-serena-y-tranquila-con-estacionamiento-privado/194097290</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1216,17 +1166,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1236,7 +1186,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1245,7 +1195,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1259,27 +1209,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1288,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1302,27 +1252,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1331,7 +1281,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1350,22 +1300,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1374,7 +1324,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1388,27 +1338,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194387339</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1417,7 +1367,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
@@ -1431,27 +1381,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>12.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1460,98 +1410,12 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="110" customHeight="1">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>13.500</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>194387339</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="110" customHeight="1">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>12.000</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>194293172</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1566,10 +1430,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,6 +484,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="752475" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -786,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1381,27 +1406,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12.000</t>
+          <t>13.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa de un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>194409634</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1410,12 +1435,55 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12.000</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>194293172</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1430,8 +1498,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -501,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -509,6 +509,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="752475" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -811,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -894,23 +919,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>21.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Casita a una cuadra del arroyo pando</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193060994</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -919,7 +948,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
         </is>
       </c>
     </row>
@@ -933,27 +962,23 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -962,7 +987,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -976,27 +1001,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>194405738</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1005,7 +1030,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1054,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1039,7 +1064,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194405738</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1048,7 +1073,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
         </is>
       </c>
     </row>
@@ -1062,27 +1087,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1091,7 +1116,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1105,27 +1130,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1134,7 +1159,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1148,27 +1173,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1177,7 +1202,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1191,27 +1216,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1220,7 +1245,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1234,27 +1259,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1263,7 +1288,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1307,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1297,7 +1322,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1306,7 +1331,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1350,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1349,7 +1374,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1363,27 +1388,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194387339</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1392,7 +1417,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1406,27 +1431,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de un dormitorio en barros blancos</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194409634</t>
+          <t>194387339</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1435,7 +1460,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
@@ -1449,27 +1474,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12.000</t>
+          <t>13.000</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa de un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>194409634</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
@@ -1478,12 +1503,55 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12.000</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>194293172</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1499,8 +1567,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -501,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -509,31 +509,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="752475" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -836,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -919,27 +894,23 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>21.000</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Casita a una cuadra del arroyo pando</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>193060994</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -948,7 +919,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -962,23 +933,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -987,7 +962,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -1001,27 +976,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194405738</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1030,7 +1005,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1029,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1064,7 +1039,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>194405738</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1073,7 +1048,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1087,27 +1062,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1116,7 +1091,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1130,27 +1105,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1159,7 +1134,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1173,27 +1148,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1202,7 +1177,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1216,27 +1191,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1245,7 +1220,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1259,27 +1234,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1288,7 +1263,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1282,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1322,7 +1297,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1331,7 +1306,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1350,22 +1325,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1374,7 +1349,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1388,27 +1363,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194387339</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1417,7 +1392,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
@@ -1431,27 +1406,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>13.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler casa de un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194387339</t>
+          <t>194409634</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1460,7 +1435,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
         </is>
       </c>
     </row>
@@ -1474,27 +1449,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13.000</t>
+          <t>12.000</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de un dormitorio en barros blancos</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>194409634</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
@@ -1503,55 +1478,12 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="110" customHeight="1">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>12.000</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>194293172</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1567,9 +1499,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,31 +484,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="752475" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -811,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -986,7 +961,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -996,7 +971,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>194405738</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1005,7 +980,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1019,27 +994,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1048,7 +1023,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1062,27 +1037,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1091,7 +1066,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1105,27 +1080,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1134,7 +1109,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1148,27 +1123,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1177,7 +1152,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1191,27 +1166,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1220,7 +1195,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1214,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1254,7 +1229,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1263,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1282,22 +1257,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1306,7 +1281,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1320,27 +1295,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194387339</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1349,7 +1324,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
@@ -1363,27 +1338,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>13.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler casa de un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194387339</t>
+          <t>194409634</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1392,7 +1367,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
         </is>
       </c>
     </row>
@@ -1406,27 +1381,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.000</t>
+          <t>12.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de un dormitorio en barros blancos</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194409634</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1435,55 +1410,12 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="110" customHeight="1">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>12.000</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>194293172</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1498,9 +1430,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1714500" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,6 +484,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="752475" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -786,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -874,18 +899,22 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Alquiler casa 1 dormitorio colonia nicolich patio y garaje</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Barrio Colonia Nicolich, Calle Bernardo O´higgins, Esquina Jose Gervasio Artigas,  Bien ubicado frente a plaza de deportes, a 2 cuadras de parada de omnibus por Ruta 101 y de Ruta interbalnearea. en zona son servicios y locomoción disponible a pasos   Cómoda Casa en Ph al frente, distribuida en una planta, segura con rejas en todas sus aberturas en terreno cerrado con camaras de seguridad  . Living Comedor amplio y luminoso  . Cocina integrada con placares  . 1 Dormitorios   . Baño funcional con conexión para lavarropas  . Garaje   . Patio de uso compartido   Superficie Total: 50m2  Precio: $20.000  Gastos Comunes: Ute y Ose se pagan aparte (único contador que se divide entre 3 casas)  Garantías: Aseguradoras o Depósito  Acepta Mascotas pequeñas   Contrato a 1 año como mínimo   Para coordinar visita por esta o mas propiedades no dude en comunicarse, podemos ayudarle a encontrar lo que está buscando.  Referencia Interna : Tera-7156</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>194425046</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -894,7 +923,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-1-dormitorio-colonia-nicolich-patio-y-garaje/194425046</t>
         </is>
       </c>
     </row>
@@ -908,27 +937,23 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -937,7 +962,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -951,27 +976,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -980,7 +1005,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -994,27 +1019,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1023,7 +1048,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1037,27 +1062,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1066,7 +1091,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1080,27 +1105,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1109,7 +1134,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1123,27 +1148,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1152,7 +1177,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1191,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1195,7 +1220,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1239,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1229,7 +1254,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1238,7 +1263,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1257,22 +1282,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1281,7 +1306,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1295,27 +1320,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>194387339</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1324,7 +1349,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1338,27 +1363,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de un dormitorio en barros blancos</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194409634</t>
+          <t>194387339</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1367,7 +1392,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
@@ -1381,27 +1406,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12.000</t>
+          <t>13.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa de un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>194409634</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1410,12 +1435,55 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12.000</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>194293172</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1430,8 +1498,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -501,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -509,6 +509,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="752475" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -811,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1029,7 +1054,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1039,7 +1064,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194405738</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1048,7 +1073,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
         </is>
       </c>
     </row>
@@ -1062,27 +1087,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1091,7 +1116,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1105,27 +1130,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>17.900</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>194213123</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1134,7 +1159,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
@@ -1148,27 +1173,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1177,7 +1202,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1191,27 +1216,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1220,7 +1245,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1234,27 +1259,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1263,7 +1288,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1307,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1297,7 +1322,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194305359</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1306,7 +1331,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1350,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1349,7 +1374,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1363,27 +1388,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194387339</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1392,7 +1417,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1406,27 +1431,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de un dormitorio en barros blancos</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194409634</t>
+          <t>194387339</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1435,7 +1460,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
@@ -1449,27 +1474,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12.000</t>
+          <t>13.000</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa de un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>194409634</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
@@ -1478,12 +1503,55 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12.000</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>194293172</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1499,8 +1567,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,10 @@
     <font>
       <color rgb="000563C1"/>
       <u val="single"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0095A5A6"/>
     </font>
   </fonts>
   <fills count="3">
@@ -77,9 +81,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -173,10 +180,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1714500" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -198,10 +205,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -223,10 +230,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -248,10 +255,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -273,10 +280,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -298,10 +305,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -323,7 +330,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1781175" cy="1333500"/>
@@ -348,10 +355,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -373,10 +380,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -398,7 +405,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1628775" cy="1333500"/>
@@ -423,10 +430,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -448,10 +455,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -473,10 +480,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -498,10 +505,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -509,31 +516,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="752475" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -910,641 +892,645 @@
       </c>
     </row>
     <row r="2" ht="110" customHeight="1">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sin imagen</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>20.000</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Alquiler casa 1 dormitorio colonia nicolich patio y garaje</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Barrio Colonia Nicolich, Calle Bernardo O´higgins, Esquina Jose Gervasio Artigas,  Bien ubicado frente a plaza de deportes, a 2 cuadras de parada de omnibus por Ruta 101 y de Ruta interbalnearea. en zona son servicios y locomoción disponible a pasos   Cómoda Casa en Ph al frente, distribuida en una planta, segura con rejas en todas sus aberturas en terreno cerrado con camaras de seguridad  . Living Comedor amplio y luminoso  . Cocina integrada con placares  . 1 Dormitorios   . Baño funcional con conexión para lavarropas  . Garaje   . Patio de uso compartido   Superficie Total: 50m2  Precio: $20.000  Gastos Comunes: Ute y Ose se pagan aparte (único contador que se divide entre 3 casas)  Garantías: Aseguradoras o Depósito  Acepta Mascotas pequeñas   Contrato a 1 año como mínimo   Para coordinar visita por esta o mas propiedades no dude en comunicarse, podemos ayudarle a encontrar lo que está buscando.  Referencia Interna : Tera-7156</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>194425046</t>
         </is>
       </c>
-      <c r="I2" s="2" t="b">
+      <c r="I2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-1-dormitorio-colonia-nicolich-patio-y-garaje/194425046</t>
         </is>
       </c>
     </row>
     <row r="3" ht="110" customHeight="1">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>20.000</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>194090773</t>
         </is>
       </c>
-      <c r="I3" s="2" t="b">
+      <c r="I3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
     <row r="4" ht="110" customHeight="1">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>19.500</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>193800861</t>
         </is>
       </c>
-      <c r="I4" s="2" t="b">
+      <c r="I4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
     <row r="5" ht="110" customHeight="1">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>19.000</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>194405738</t>
         </is>
       </c>
-      <c r="I5" s="2" t="b">
+      <c r="I5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
         </is>
       </c>
     </row>
     <row r="6" ht="110" customHeight="1">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>19.000</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>193981913</t>
         </is>
       </c>
-      <c r="I6" s="2" t="b">
+      <c r="I6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
     <row r="7" ht="110" customHeight="1">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>17.900</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>194213123</t>
         </is>
       </c>
-      <c r="I7" s="2" t="b">
+      <c r="I7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
     <row r="8" ht="110" customHeight="1">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>17.000</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>194185464</t>
         </is>
       </c>
-      <c r="I8" s="2" t="b">
+      <c r="I8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
     <row r="9" ht="110" customHeight="1">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>15.900</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>193775027</t>
         </is>
       </c>
-      <c r="I9" s="2" t="b">
+      <c r="I9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
     <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>15.500</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>190297262</t>
         </is>
       </c>
-      <c r="I10" s="2" t="b">
+      <c r="I10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
     <row r="11" ht="110" customHeight="1">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>15.000</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Casa en alquiler</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>194305359</t>
         </is>
       </c>
-      <c r="I11" s="2" t="b">
+      <c r="I11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
     <row r="12" ht="110" customHeight="1">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>15.000</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>193627120</t>
         </is>
       </c>
-      <c r="I12" s="2" t="b">
+      <c r="I12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
     <row r="13" ht="110" customHeight="1">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>15.000</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>193878393</t>
         </is>
       </c>
-      <c r="I13" s="2" t="b">
+      <c r="I13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
     <row r="14" ht="110" customHeight="1">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>13.500</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>194387339</t>
         </is>
       </c>
-      <c r="I14" s="2" t="b">
+      <c r="I14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
     <row r="15" ht="110" customHeight="1">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>13.000</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Alquiler casa de un dormitorio en barros blancos</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>194409634</t>
         </is>
       </c>
-      <c r="I15" s="2" t="b">
+      <c r="I15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
         </is>
       </c>
     </row>
     <row r="16" ht="110" customHeight="1">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>12.000</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>194293172</t>
         </is>
       </c>
-      <c r="I16" s="2" t="b">
+      <c r="I16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,10 +35,6 @@
     <font>
       <color rgb="000563C1"/>
       <u val="single"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="0095A5A6"/>
     </font>
   </fonts>
   <fills count="3">
@@ -81,12 +77,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -180,10 +173,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1714500" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -205,10 +198,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -230,10 +223,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -255,10 +248,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -280,10 +273,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -305,10 +298,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1876425" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -330,7 +323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1781175" cy="1333500"/>
@@ -355,10 +348,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -380,10 +373,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -405,7 +398,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1628775" cy="1333500"/>
@@ -430,10 +423,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -455,10 +448,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -480,10 +473,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -505,10 +498,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -516,6 +509,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="752475" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -892,645 +910,641 @@
       </c>
     </row>
     <row r="2" ht="110" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Sin imagen</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>20.000</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Alquiler casa 1 dormitorio colonia nicolich patio y garaje</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Barrio Colonia Nicolich, Calle Bernardo O´higgins, Esquina Jose Gervasio Artigas,  Bien ubicado frente a plaza de deportes, a 2 cuadras de parada de omnibus por Ruta 101 y de Ruta interbalnearea. en zona son servicios y locomoción disponible a pasos   Cómoda Casa en Ph al frente, distribuida en una planta, segura con rejas en todas sus aberturas en terreno cerrado con camaras de seguridad  . Living Comedor amplio y luminoso  . Cocina integrada con placares  . 1 Dormitorios   . Baño funcional con conexión para lavarropas  . Garaje   . Patio de uso compartido   Superficie Total: 50m2  Precio: $20.000  Gastos Comunes: Ute y Ose se pagan aparte (único contador que se divide entre 3 casas)  Garantías: Aseguradoras o Depósito  Acepta Mascotas pequeñas   Contrato a 1 año como mínimo   Para coordinar visita por esta o mas propiedades no dude en comunicarse, podemos ayudarle a encontrar lo que está buscando.  Referencia Interna : Tera-7156</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>194425046</t>
         </is>
       </c>
-      <c r="I2" s="3" t="b">
+      <c r="I2" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-1-dormitorio-colonia-nicolich-patio-y-garaje/194425046</t>
         </is>
       </c>
     </row>
     <row r="3" ht="110" customHeight="1">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>20.000</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>194090773</t>
         </is>
       </c>
-      <c r="I3" s="3" t="b">
+      <c r="I3" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
     <row r="4" ht="110" customHeight="1">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>19.500</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>193800861</t>
         </is>
       </c>
-      <c r="I4" s="3" t="b">
+      <c r="I4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
     <row r="5" ht="110" customHeight="1">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>19.000</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>194405738</t>
         </is>
       </c>
-      <c r="I5" s="3" t="b">
+      <c r="I5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
         </is>
       </c>
     </row>
     <row r="6" ht="110" customHeight="1">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>19.000</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>193981913</t>
         </is>
       </c>
-      <c r="I6" s="3" t="b">
+      <c r="I6" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
     <row r="7" ht="110" customHeight="1">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>17.900</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>194213123</t>
         </is>
       </c>
-      <c r="I7" s="3" t="b">
+      <c r="I7" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
         </is>
       </c>
     </row>
     <row r="8" ht="110" customHeight="1">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>17.000</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>194185464</t>
         </is>
       </c>
-      <c r="I8" s="3" t="b">
+      <c r="I8" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
     <row r="9" ht="110" customHeight="1">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>15.900</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>193775027</t>
         </is>
       </c>
-      <c r="I9" s="3" t="b">
+      <c r="I9" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
     <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>15.500</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>190297262</t>
         </is>
       </c>
-      <c r="I10" s="3" t="b">
+      <c r="I10" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
     <row r="11" ht="110" customHeight="1">
-      <c r="A11" s="3" t="inlineStr"/>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>15.000</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Casa en alquiler</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>194305359</t>
         </is>
       </c>
-      <c r="I11" s="3" t="b">
+      <c r="I11" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
         </is>
       </c>
     </row>
     <row r="12" ht="110" customHeight="1">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>15.000</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>193627120</t>
         </is>
       </c>
-      <c r="I12" s="3" t="b">
+      <c r="I12" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
     <row r="13" ht="110" customHeight="1">
-      <c r="A13" s="3" t="inlineStr"/>
-      <c r="B13" s="3" t="inlineStr"/>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>15.000</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>193878393</t>
         </is>
       </c>
-      <c r="I13" s="3" t="b">
+      <c r="I13" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
     <row r="14" ht="110" customHeight="1">
-      <c r="A14" s="3" t="inlineStr"/>
-      <c r="B14" s="3" t="inlineStr"/>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>13.500</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>194387339</t>
         </is>
       </c>
-      <c r="I14" s="3" t="b">
+      <c r="I14" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
     <row r="15" ht="110" customHeight="1">
-      <c r="A15" s="3" t="inlineStr"/>
-      <c r="B15" s="3" t="inlineStr"/>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>13.000</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Alquiler casa de un dormitorio en barros blancos</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>194409634</t>
         </is>
       </c>
-      <c r="I15" s="3" t="b">
+      <c r="I15" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
         </is>
       </c>
     </row>
     <row r="16" ht="110" customHeight="1">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr"/>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>12.000</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>194293172</t>
         </is>
       </c>
-      <c r="I16" s="3" t="b">
+      <c r="I16" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1876425" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,56 +484,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1781175" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="752475" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -836,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -987,7 +937,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/coloniacasa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/colonia-casa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -1130,27 +1080,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa de 1 dormitorio en neptunia sur. gran terreno</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Alquiler  Casa de 1 dormitorio en Neptunia Sur, Canelones. Próximo a la ruta interbalnearia al Sur. A pocas cuadras del Arroyo y a minutos de la Playa. Terreno de 488m2 con tejido perimetral. Construcción de steel framing a estrenar.Casa con living comedor al frente con cocina integrada. Dormitorio de aproximadamente 3m x 4m con ventanal al frente y ventana al contrafrente. Baño completo. Se destaca por tener muchas ventanas que le permiten una excelente ventilación e ingreso de luz natural.Garantías: Portoseguro, Sura o SBI. Te asesoramos con la tramitación!Alquiler mínimo de 1 año.Comisión inmobiliaria: 1 mes de alquiler + IVA.-AHO8492420 - Abate Propiedades - Gestionamos tu garantía de alquiler. Somos corredores de seguros de SURA - PORTO - SBI - SANCOR - ZURICH SANTANDER - MAPFRE.</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194213123</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1159,7 +1109,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-de-1-dormitorio-en-neptunia-sur-gran-terreno/194213123</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1173,27 +1123,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1202,7 +1152,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1216,27 +1166,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1245,7 +1195,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1259,27 +1209,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1288,7 +1238,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1307,22 +1257,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 2 dorm. Neptunia Nte.  Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>194305359</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1331,7 +1281,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler/194305359</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1345,27 +1295,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de  Av. Los Pinos. 2 dormitorios - 2 baños Cocina - Living comedor Patio al frente Patio al fondo Lugar para auto $ 15.000 gtía : Aseguradoras Acepta mascota El 80% de la casa no tiene cieloraso Coordine visita Comisión inm: (mes +iva)  Referencia Interna : Tera-4381</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>194387339</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1374,7 +1324,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
@@ -1388,27 +1338,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>13.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler casa de un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194409634</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1417,7 +1367,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
         </is>
       </c>
     </row>
@@ -1431,27 +1381,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>12.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194387339</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1460,98 +1410,12 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="110" customHeight="1">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>13.000</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler casa de un dormitorio en barros blancos</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>194409634</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="110" customHeight="1">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>12.000</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>194293172</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1566,10 +1430,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -484,6 +484,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="752475" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -786,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1080,27 +1105,23 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>18.000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Se alquila casa contenedor en neptunia sur</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>Se alquila casa contenedor en Neptunia sur   Living y cocina integrada   Dos dormitorios   Baño completo   Entrada compartida   Complejo de varias casas  Patio privado con parrillero  Garantía de aseguradora más mes adelantado.  $18.000   Referencia Interna : Tera-4949</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>194451860</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1109,7 +1130,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/se-alquila-casa-contenedor-en-neptunia-sur/194451860</t>
         </is>
       </c>
     </row>
@@ -1123,27 +1144,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1152,7 +1173,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1187,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1195,7 +1216,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1209,27 +1230,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1238,7 +1259,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1257,22 +1278,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1281,7 +1302,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1295,27 +1316,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>194387339</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1324,7 +1345,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1338,27 +1359,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de un dormitorio en barros blancos</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194409634</t>
+          <t>194387339</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1367,7 +1388,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
@@ -1381,27 +1402,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12.000</t>
+          <t>13.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa de un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>194409634</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1410,12 +1431,55 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12.000</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>194293172</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1430,8 +1494,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1714500" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -209,6 +209,306 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1009650" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1781175" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1800225" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="752475" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1781175" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1781175" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="600075" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1628775" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="752475" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1781175" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="752475" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -511,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -594,27 +894,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Alquiler casa 1 dormitorio colonia nicolich patio y garaje</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
+          <t>Barrio Colonia Nicolich, Calle Bernardo O´higgins, Esquina Jose Gervasio Artigas,  Bien ubicado frente a plaza de deportes, a 2 cuadras de parada de omnibus por Ruta 101 y de Ruta interbalnearea. en zona son servicios y locomoción disponible a pasos   Cómoda Casa en Ph al frente, distribuida en una planta, segura con rejas en todas sus aberturas en terreno cerrado con camaras de seguridad  . Living Comedor amplio y luminoso  . Cocina integrada con placares  . 1 Dormitorios   . Baño funcional con conexión para lavarropas  . Garaje   . Patio de uso compartido   Superficie Total: 50m2  Precio: $20.000  Gastos Comunes: Ute y Ose se pagan aparte (único contador que se divide entre 3 casas)  Garantías: Aseguradoras o Depósito  Acepta Mascotas pequeñas   Contrato a 1 año como mínimo   Para coordinar visita por esta o mas propiedades no dude en comunicarse, podemos ayudarle a encontrar lo que está buscando.  Referencia Interna : Tera-7156</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>194405738</t>
+          <t>194425046</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -623,7 +923,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-1-dormitorio-colonia-nicolich-patio-y-garaje/194425046</t>
         </is>
       </c>
     </row>
@@ -637,27 +937,23 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -666,17 +962,541 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/colonia-casa-de-campo-el-quinton/194090773</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="110" customHeight="1">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19.500</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>193800861</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="110" customHeight="1">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19.000</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>194405738</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="110" customHeight="1">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19.000</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>193981913</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18.000</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Se alquila casa contenedor en neptunia sur</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Se alquila casa contenedor en Neptunia sur   Living y cocina integrada   Dos dormitorios   Baño completo   Entrada compartida   Complejo de varias casas  Patio privado con parrillero  Garantía de aseguradora más mes adelantado.  $18.000   Referencia Interna : Tera-4949</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>194451860</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/se-alquila-casa-contenedor-en-neptunia-sur/194451860</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17.000</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>194185464</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="110" customHeight="1">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>15.900</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>193775027</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="110" customHeight="1">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15.500</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>190297262</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="110" customHeight="1">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15.000</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>193627120</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="110" customHeight="1">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15.000</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>193878393</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="110" customHeight="1">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13.500</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>194387339</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="110" customHeight="1">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13.000</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler casa de un dormitorio en barros blancos</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>194409634</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12.000</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>194293172</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -1118,7 +1118,11 @@
           <t>Se alquila casa contenedor en Neptunia sur   Living y cocina integrada   Dos dormitorios   Baño completo   Entrada compartida   Complejo de varias casas  Patio privado con parrillero  Garantía de aseguradora más mes adelantado.  $18.000   Referencia Interna : Tera-4949</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>194451860</t>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1714500" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1714500" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -501,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -509,6 +509,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="752475" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -811,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -894,27 +919,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>21.000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 1 dormitorio colonia nicolich patio y garaje</t>
+          <t>Casita a una cuadra del arroyo pando</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Barrio Colonia Nicolich, Calle Bernardo O´higgins, Esquina Jose Gervasio Artigas,  Bien ubicado frente a plaza de deportes, a 2 cuadras de parada de omnibus por Ruta 101 y de Ruta interbalnearea. en zona son servicios y locomoción disponible a pasos   Cómoda Casa en Ph al frente, distribuida en una planta, segura con rejas en todas sus aberturas en terreno cerrado con camaras de seguridad  . Living Comedor amplio y luminoso  . Cocina integrada con placares  . 1 Dormitorios   . Baño funcional con conexión para lavarropas  . Garaje   . Patio de uso compartido   Superficie Total: 50m2  Precio: $20.000  Gastos Comunes: Ute y Ose se pagan aparte (único contador que se divide entre 3 casas)  Garantías: Aseguradoras o Depósito  Acepta Mascotas pequeñas   Contrato a 1 año como mínimo   Para coordinar visita por esta o mas propiedades no dude en comunicarse, podemos ayudarle a encontrar lo que está buscando.  Referencia Interna : Tera-7156</t>
+          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>194425046</t>
+          <t>193060994</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -923,7 +948,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-1-dormitorio-colonia-nicolich-patio-y-garaje/194425046</t>
+          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
         </is>
       </c>
     </row>
@@ -942,18 +967,22 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Alquiler casa 1 dormitorio colonia nicolich patio y garaje</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Barrio Colonia Nicolich, Calle Bernardo O´higgins, Esquina Jose Gervasio Artigas,  Bien ubicado frente a plaza de deportes, a 2 cuadras de parada de omnibus por Ruta 101 y de Ruta interbalnearea. en zona son servicios y locomoción disponible a pasos   Cómoda Casa en Ph al frente, distribuida en una planta, segura con rejas en todas sus aberturas en terreno cerrado con camaras de seguridad  . Living Comedor amplio y luminoso  . Cocina integrada con placares  . 1 Dormitorios   . Baño funcional con conexión para lavarropas  . Garaje   . Patio de uso compartido   Superficie Total: 50m2  Precio: $20.000  Gastos Comunes: Ute y Ose se pagan aparte (único contador que se divide entre 3 casas)  Garantías: Aseguradoras o Depósito  Acepta Mascotas pequeñas   Contrato a 1 año como mínimo   Para coordinar visita por esta o mas propiedades no dude en comunicarse, podemos ayudarle a encontrar lo que está buscando.  Referencia Interna : Tera-7156</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>194425046</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -962,7 +991,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/colonia-casa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-1-dormitorio-colonia-nicolich-patio-y-garaje/194425046</t>
         </is>
       </c>
     </row>
@@ -976,27 +1005,23 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1005,7 +1030,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/colonia-casa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -1019,27 +1044,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>194405738</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1048,7 +1073,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1097,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1082,7 +1107,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194405738</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1091,7 +1116,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
         </is>
       </c>
     </row>
@@ -1105,27 +1130,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18.000</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Se alquila casa contenedor en neptunia sur</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Se alquila casa contenedor en Neptunia sur   Living y cocina integrada   Dos dormitorios   Baño completo   Entrada compartida   Complejo de varias casas  Patio privado con parrillero  Garantía de aseguradora más mes adelantado.  $18.000   Referencia Interna : Tera-4949</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194451860</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1134,7 +1159,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/se-alquila-casa-contenedor-en-neptunia-sur/194451860</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1148,27 +1173,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>18.000</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Se alquila casa contenedor en neptunia sur</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>Se alquila casa contenedor en Neptunia sur   Living y cocina integrada   Dos dormitorios   Baño completo   Entrada compartida   Complejo de varias casas  Patio privado con parrillero  Garantía de aseguradora más mes adelantado.  $18.000   Referencia Interna : Tera-4949</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>194451860</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1177,7 +1202,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/se-alquila-casa-contenedor-en-neptunia-sur/194451860</t>
         </is>
       </c>
     </row>
@@ -1191,27 +1216,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad.? Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.000Una opción accesible, cómoda y segura para vivir. (CW250513)</t>
+          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194185464</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1220,7 +1245,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
         </is>
       </c>
     </row>
@@ -1234,27 +1259,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad. Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.500Una opción accesible, cómoda y segura para vivir.Sincronizada desde Casasweb.com ref: CW250513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1263,7 +1288,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1302,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1306,7 +1331,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1350,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1349,7 +1374,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1363,27 +1388,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194387339</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1392,7 +1417,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1406,27 +1431,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de un dormitorio en barros blancos</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194409634</t>
+          <t>194387339</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1435,7 +1460,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
@@ -1449,27 +1474,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12.000</t>
+          <t>13.000</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa de un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>194409634</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
@@ -1478,12 +1503,55 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12.000</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>194293172</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1499,8 +1567,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -501,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -509,31 +509,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="752475" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -836,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1216,27 +1191,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler 2 dormitorios en colonia nicolich</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>EN COMPLEJO DE CASAS CONTENEDOR !  Sin gastos comunes Living comedor Cocina semi integrada 2 Dormitorios 1 Baño completo Jardin al frente Lugar para auto GARANTIAS Anda, Contaduria o Porto Seguro</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad. Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.500Una opción accesible, cómoda y segura para vivir.Sincronizada desde Casasweb.com ref: CW250513</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>194185464</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1245,7 +1220,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-2-dormitorios-en-colonia-nicolich/194185464</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1259,27 +1234,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad. Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.500Una opción accesible, cómoda y segura para vivir.Sincronizada desde Casasweb.com ref: CW250513</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1288,7 +1263,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1302,27 +1277,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1331,7 +1306,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1350,22 +1325,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1374,7 +1349,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1388,27 +1363,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>194387339</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1417,7 +1392,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
@@ -1431,27 +1406,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>13.000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler casa de un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194387339</t>
+          <t>194409634</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1460,7 +1435,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
         </is>
       </c>
     </row>
@@ -1474,27 +1449,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13.000</t>
+          <t>12.000</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de un dormitorio en barros blancos</t>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>194409634</t>
+          <t>194293172</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
@@ -1503,55 +1478,12 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="110" customHeight="1">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>12.000</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>194293172</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1567,9 +1499,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
 </worksheet>
 </file>
--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -201,7 +201,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1714500" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1009650" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1009650" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1714500" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -942,22 +942,18 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 1 dormitorio colonia nicolich patio y garaje</t>
+          <t>Colonia-casa de campo el quinton</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Barrio Colonia Nicolich, Calle Bernardo O´higgins, Esquina Jose Gervasio Artigas,  Bien ubicado frente a plaza de deportes, a 2 cuadras de parada de omnibus por Ruta 101 y de Ruta interbalnearea. en zona son servicios y locomoción disponible a pasos   Cómoda Casa en Ph al frente, distribuida en una planta, segura con rejas en todas sus aberturas en terreno cerrado con camaras de seguridad  . Living Comedor amplio y luminoso  . Cocina integrada con placares  . 1 Dormitorios   . Baño funcional con conexión para lavarropas  . Garaje   . Patio de uso compartido   Superficie Total: 50m2  Precio: $20.000  Gastos Comunes: Ute y Ose se pagan aparte (único contador que se divide entre 3 casas)  Garantías: Aseguradoras o Depósito  Acepta Mascotas pequeñas   Contrato a 1 año como mínimo   Para coordinar visita por esta o mas propiedades no dude en comunicarse, podemos ayudarle a encontrar lo que está buscando.  Referencia Interna : Tera-7156</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>194425046</t>
+          <t>194090773</t>
         </is>
       </c>
       <c r="I3" s="2" t="b">
@@ -966,7 +962,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-1-dormitorio-colonia-nicolich-patio-y-garaje/194425046</t>
+          <t>https://www.infocasas.com.uy/colonia-casa-de-campo-el-quinton/194090773</t>
         </is>
       </c>
     </row>
@@ -980,23 +976,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Colonia-casa de campo el quinton</t>
+          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>HERMOSA CASA DE CAMPO EN ALQUILER – EL QUINTÓN&amp;nbsp;Tranquilidad, naturaleza y mucho espacio verde para disfrutar.Se alquila hermosa casa de campo ubicada en El Quintón, rodeada de naturaleza y emplazada en un gran predio con amplios espacios verdes, ideal para quienes buscan alejarse del ruido y disfrutar de un entorno tranquilo y natural.La propiedad ofrece un ambiente cálido y confortable, con todo el encanto de la vida de campo y amplios espacios exteriores para disfrutar en familia, descansar y conectar con la naturaleza.Un lugar ideal para quienes valoran la privacidad, la tranquilidad y el contacto con el verde, sin resignar la comodidad de contar con una vivienda acogedora.&amp;nbsp;Una oportunidad para vivir el campo y disfrutar de otra calidad de vida.&amp;nbsp;Consultanos para conocer más detalles y coordinar una visita.Código de referencia: GHO8596688Si te interesó la propiedad puedes coordinar visita a través de los números: ALQUILERES:  Oficina *** / *** VENTAS: *** (Martín González)/ *** (Carlos Véliz)Estamos ubicados en Uruguay esquina Roosevelt, Carmelo - Uruguay.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>194090773</t>
+          <t>193800861</t>
         </is>
       </c>
       <c r="I4" s="2" t="b">
@@ -1005,7 +1005,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/colonia-casa-de-campo-el-quinton/194090773</t>
+          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
         </is>
       </c>
     </row>
@@ -1019,27 +1019,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Monoambiente en alquiler | casa en neptunia con chimenea y jardín</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Esta encantadora cabaña en Neptunia ofrece un refugio acogedor donde cada rincón invita a la tranquilidad. Con 30 m² de espacio perfectamente distribuidos, disfrutarás de ambientes iluminados y cálidos, ideales para relajarte después de un largo día. La chimenea añade un toque especial, creando un ambiente perfecto para compartir momentos inolvidables. Además, el acceso a internet y la cocina equipada garantizan que tu comodidad esté siempre presente, mientras que la cercanía a áreas verdes permite disfrutar de la naturaleza sin salir de casa. Características Destacadas: Ambientes acogedores y luminosos Chimenea para días fríos Acceso a internet disponible Admite mascotas Ubicación tranquila y accesible GASTOS COMUNES : $2900</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193800861</t>
+          <t>194405738</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1048,7 +1048,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/monoambiente-en-alquiler-casa-en-neptunia-con-chimenea-y-jardin/193800861</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>194405738</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1091,7 +1091,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1105,27 +1105,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>18.000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Se alquila casa contenedor en neptunia sur</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Se alquila casa contenedor en Neptunia sur   Living y cocina integrada   Dos dormitorios   Baño completo   Entrada compartida   Complejo de varias casas  Patio privado con parrillero  Garantía de aseguradora más mes adelantado.  $18.000   Referencia Interna : Tera-4949</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194451860</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1134,7 +1134,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/se-alquila-casa-contenedor-en-neptunia-sur/194451860</t>
         </is>
       </c>
     </row>
@@ -1153,22 +1153,22 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Se alquila casa contenedor en neptunia sur</t>
+          <t>Alquiler casa 1 dormitorio colonia nicolich patio y garaje</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Se alquila casa contenedor en Neptunia sur   Living y cocina integrada   Dos dormitorios   Baño completo   Entrada compartida   Complejo de varias casas  Patio privado con parrillero  Garantía de aseguradora más mes adelantado.  $18.000   Referencia Interna : Tera-4949</t>
+          <t>Barrio Colonia Nicolich, Calle Bernardo O´higgins, Esquina Jose Gervasio Artigas,  Bien ubicado frente a plaza de deportes, a 2 cuadras de parada de omnibus por Ruta 101 y de Ruta interbalnearea. en zona son servicios y locomoción disponible a pasos   Cómoda Casa en Ph al frente, distribuida en una planta, segura con rejas en todas sus aberturas en terreno cerrado con camaras de seguridad  . Living Comedor amplio y luminoso  . Cocina integrada con placares  . 1 Dormitorios   . Baño funcional con conexión para lavarropas  . Garaje   . Patio de uso compartido   Superficie Total: 50m2  Precio: $18.000  Gastos Comunes: Ute y Ose se pagan aparte (único contador que se divide entre 3 casas)  Garantías: Aseguradoras o Depósito  Acepta Mascotas pequeñas   Contrato a 1 año como mínimo   Para coordinar visita por esta o mas propiedades no dude en comunicarse, podemos ayudarle a encontrar lo que está buscando.  Referencia Interna : Tera-7156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194451860</t>
+          <t>194425046</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1177,7 +1177,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/se-alquila-casa-contenedor-en-neptunia-sur/194451860</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-1-dormitorio-colonia-nicolich-patio-y-garaje/194425046</t>
         </is>
       </c>
     </row>

--- a/alquileres.xlsx
+++ b/alquileres.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Alquileres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alquileres'!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="1885950" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -251,7 +251,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1000125" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -276,7 +276,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1800225" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1800225" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -326,7 +326,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1714500" cy="1333500"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -351,7 +351,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1714500" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -376,7 +376,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="600075" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1628775" cy="1333500"/>
+    <ext cx="600075" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -426,7 +426,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1628775" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -451,7 +451,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1266825"/>
+    <ext cx="752475" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -476,7 +476,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1781175" cy="1333500"/>
+    <ext cx="1905000" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -501,7 +501,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="752475" cy="1333500"/>
+    <ext cx="1781175" cy="1333500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -509,6 +509,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="752475" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -811,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -887,34 +912,26 @@
     <row r="2" ht="110" customHeight="1">
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>21.000</t>
-        </is>
-      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Casita a una cuadra del arroyo pando</t>
+          <t>Casa en alquiler</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Casita con entrepiso a media cuadra del Arroyo Pando.&amp;nbsp;Amplio mono ambiente con jardín privado. A cuatro cuadras del Peaje Pando. Fácil&amp;nbsp;acceso a&amp;nbsp;Montevideo y el Este con transporte público.&amp;nbsp;Tiene estufa a leña.&amp;nbsp;Tranquilo vecindario.&amp;nbsp;IMPORTANTE INFORMACIÓN:21.000 por mesSe paga mes adelantado.Garantía preferida - cuatro meses de alquiler&amp;nbsp;OSE y UTE compartido con casita del fondo (mes de Septiembre $2450)CONTACTARSE AL ***</t>
+          <t>INMOBILIARIA MONYMAR  RUTA 101 KM 29 Y CAMINO EL GALLO ....PROYECTO A MEDIDA "LLAVE EN MANO" CON CONTRATOS A LARGO PLAZO....PROYECTOS DE 1000m2 a 18.000m2.... CONSULTE Y LE HACEMOS EL DEPOSITO QUE UD. NECESITA!!...YA SE HAN INSTALADO MULTINACIONALES DE DIVERSOS RUBROS BAJO ESE FORMATO (Laboratorios, Consumo masivo)....  LOCAL GALPON A ESTRENAR..... FORME PARTE DE UN GRAN POLO LOGÍSTICO E INDUSTRIAL CON TODOS LOS SERVICIOS: Vigilancia 24hs y control de acceso. Cámaras de vigilancia en todo el predio. Iluminación perimetral y cerca eléctrica. Red central de incendios con reserva de agua superior a la exigida por Bomberos. Mantenimiento de áreas verdes. Limpieza de áreas comunes. Recolección de aguas negras. Posibilidad de prestar servicio de operador logístico. Además cuenta con todo el equipamiento para la habilitación de bomberos (el inquilino debe obtenerla a su nombre)..... EL PARQUE LOGÍSTICO CUENTA CON FACIL ACCESO A TODAS LA RUTAS NACIONALES: a 3 km de Ruta 8 (salida a Brasil), a 7 km Anillo Perimetral, conectando a  Ruta 1 (salida a Argentina). A 8 km de  Ruta Interbalnearia (salida hacia el Este).  CONSULTE  (LO60510).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>193060994</t>
+          <t>194482896</t>
         </is>
       </c>
       <c r="I2" s="2" t="b">
@@ -923,7 +940,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casita-a-una-cuadra-del-arroyo-pando/193060994</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler/194482896</t>
         </is>
       </c>
     </row>
@@ -1024,22 +1041,18 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
+          <t>Onex alquila ph en neptunia sur</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>ONEX ALQUILA | Casa PH en Neptunia Sur ?  A solo 100 metros del mar, ideal para quienes buscan tranquilidad y cercanía a la playa.  ✔️ 1 dormitorio  ✔️ 1 baño  ✔️ Cocina integrada  ✔️ Living comedor  ✔️ Entrada compartida  ? Alquiler: $19.000  ✅ Gastos comunes incluidos (mantenimiento de espacios verdes y pozo)  ? Garantías: ANDA, CGN o aseguradoras  ? Comisión inmobiliaria: 1 mes + IVA  ? Consultá y coordiná tu visita con nuestros asesores  Referencia Interna : Tera-4485</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>194405738</t>
+          <t>194482726</t>
         </is>
       </c>
       <c r="I5" s="2" t="b">
@@ -1048,7 +1061,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
+          <t>https://www.infocasas.com.uy/onex-alquila-ph-en-neptunia-sur/194482726</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1085,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
+          <t>Descubre la comodidad y el estilo en esta casa de 1 dormitorio a estrenar en Aeroparque, ideal para quienes buscan un espacio acogedor y luminoso.   La propiedad cuenta con un amplio living comedor integrado a la cocina, perfecto para disfrutar de momentos agradables. El dormitorio, con una amplia ventana, ofrece excelente iluminación natural. Además, cuenta con un baño completo, patio, y un amplio frente y fondo propio, brindando un espacio exterior ideal para relajarse. Su ubicación es estratégica, cercana a centros educativos, comercios y paradas de ómnibus, a solo 3 cuadras de la ruta 101.   Características de la propiedad: -Traspaso alquiler, contrato por 1 año - Superficie total: 45 m² (cubiertos) - Ambientes: 1 dormitorio, 1 baño - Cochera: descubierta - Gastos comunes: UY$1.500 - Servicios: agua corriente, calefón, campana de extracción en cocina - Orientación: norte - Antigüedad: 5 años - Garantías aceptadas: ANDA  La propiedad ideal para ti te está esperando! No dejes pasar esta oportunidad, contactate ya! Michelle Minvielle</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1082,7 +1095,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>193981913</t>
+          <t>194405738</t>
         </is>
       </c>
       <c r="I6" s="2" t="b">
@@ -1091,7 +1104,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/194405738</t>
         </is>
       </c>
     </row>
@@ -1105,27 +1118,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18.000</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Se alquila casa contenedor en neptunia sur</t>
+          <t>Casa en alquiler c/ cochera en villa aeroparque</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Se alquila casa contenedor en Neptunia sur   Living y cocina integrada   Dos dormitorios   Baño completo   Entrada compartida   Complejo de varias casas  Patio privado con parrillero  Garantía de aseguradora más mes adelantado.  $18.000   Referencia Interna : Tera-4949</t>
+          <t>Casa a estrenar en alquiler, ubicada en la calle Braniff, en Villa Aeroparque. Este inmueble se encuentra a tan solo 3 cuadras de la ruta 101, ofreciendo una excelente conectividad y acceso a los principales puntos de interés de la zona. Con una superficie total de 45 m², esta propiedad incluye un dormitorio con hermoso ventanal, un baño y una cocina funcional. La orientación norte asegura una luminosidad natural durante todo el día.Diseñada para el confort, la casa está equipada con aire acondicionado, conexión para lavarropas y agua corriente. Además, cuenta con un espacio exterior que incluye un jardín, ideal para disfrutar de momentos al aire libre. La cochera descubierta proporciona comodidad y facilidad de acceso. Esta propiedad permite mascotas, lo que la convierte en una opción ideal para quienes buscan un hogar amigable y práctico.Con un alquiler mensual de UY$19.000, esta casa representa una oportunidad única para aquellos que buscan un espacio moderno y funcional. Perfecta para disfrutar de la tranquilidad de Villa Aeroparque, esta propiedad a estrenar es una opción atractiva para quienes valoran la calidad y el estilo de vida que ofrece esta zona.Alquiler: $19.000Garantías: Preferiblemente Anda, tambien pueden ser cgn o Aseguradoras ¡Llámenos para conocer más en detalle esta propiedad! Tel: ***Email: veronicaleal@inmobiliariaglobalpro.comGlobal Pro Negocios inmobiliarioshttps://www.inmobiliariaglobalpro.com/</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>194451860</t>
+          <t>193981913</t>
         </is>
       </c>
       <c r="I7" s="2" t="b">
@@ -1134,7 +1147,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/se-alquila-casa-contenedor-en-neptunia-sur/194451860</t>
+          <t>https://www.infocasas.com.uy/casa-en-alquiler-c-cochera-en-villa-aeroparque/193981913</t>
         </is>
       </c>
     </row>
@@ -1153,22 +1166,22 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa 1 dormitorio colonia nicolich patio y garaje</t>
+          <t>Se alquila casa contenedor en neptunia sur</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Barrio Colonia Nicolich, Calle Bernardo O´higgins, Esquina Jose Gervasio Artigas,  Bien ubicado frente a plaza de deportes, a 2 cuadras de parada de omnibus por Ruta 101 y de Ruta interbalnearea. en zona son servicios y locomoción disponible a pasos   Cómoda Casa en Ph al frente, distribuida en una planta, segura con rejas en todas sus aberturas en terreno cerrado con camaras de seguridad  . Living Comedor amplio y luminoso  . Cocina integrada con placares  . 1 Dormitorios   . Baño funcional con conexión para lavarropas  . Garaje   . Patio de uso compartido   Superficie Total: 50m2  Precio: $18.000  Gastos Comunes: Ute y Ose se pagan aparte (único contador que se divide entre 3 casas)  Garantías: Aseguradoras o Depósito  Acepta Mascotas pequeñas   Contrato a 1 año como mínimo   Para coordinar visita por esta o mas propiedades no dude en comunicarse, podemos ayudarle a encontrar lo que está buscando.  Referencia Interna : Tera-7156</t>
+          <t>Se alquila casa contenedor en Neptunia sur   Living y cocina integrada   Dos dormitorios   Baño completo   Entrada compartida   Complejo de varias casas  Patio privado con parrillero  Garantía de aseguradora más mes adelantado.  $18.000   Referencia Interna : Tera-4949</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>194425046</t>
+          <t>194451860</t>
         </is>
       </c>
       <c r="I8" s="2" t="b">
@@ -1177,7 +1190,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-1-dormitorio-colonia-nicolich-patio-y-garaje/194425046</t>
+          <t>https://www.infocasas.com.uy/se-alquila-casa-contenedor-en-neptunia-sur/194451860</t>
         </is>
       </c>
     </row>
@@ -1191,27 +1204,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15.900</t>
+          <t>18.000</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
+          <t>Alquiler casa 1 dormitorio colonia nicolich patio y garaje</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad. Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.500Una opción accesible, cómoda y segura para vivir.Sincronizada desde Casasweb.com ref: CW250513</t>
+          <t>Barrio Colonia Nicolich, Calle Bernardo O´higgins, Esquina Jose Gervasio Artigas,  Bien ubicado frente a plaza de deportes, a 2 cuadras de parada de omnibus por Ruta 101 y de Ruta interbalnearea. en zona son servicios y locomoción disponible a pasos   Cómoda Casa en Ph al frente, distribuida en una planta, segura con rejas en todas sus aberturas en terreno cerrado con camaras de seguridad  . Living Comedor amplio y luminoso  . Cocina integrada con placares  . 1 Dormitorios   . Baño funcional con conexión para lavarropas  . Garaje   . Patio de uso compartido   Superficie Total: 50m2  Precio: $18.000  Gastos Comunes: Ute y Ose se pagan aparte (único contador que se divide entre 3 casas)  Garantías: Aseguradoras o Depósito  Acepta Mascotas pequeñas   Contrato a 1 año como mínimo   Para coordinar visita por esta o mas propiedades no dude en comunicarse, podemos ayudarle a encontrar lo que está buscando.  Referencia Interna : Tera-7156</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>193775027</t>
+          <t>194425046</t>
         </is>
       </c>
       <c r="I9" s="2" t="b">
@@ -1220,7 +1233,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-1-dormitorio-colonia-nicolich-patio-y-garaje/194425046</t>
         </is>
       </c>
     </row>
@@ -1234,27 +1247,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.900</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
+          <t>Alquiler 1 dormitorio en complejo cerrado - colonia nicolich</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
+          <t>¡Nuevo complejo cerrado en Colonia Nicolich! Viví en una zona tranquila y con excelente ubicación, próximo al Aeropuerto, en un moderno complejo de contenedores diseñado para brindar comodidad, seguridad y practicidad. Unidades de 1 dormitorio Complejo cerrado Parrillero individual Lugar para auto Diseño moderno y funcional Ideal para una o dos personas Ubicado en Colonia Nicolich, Canelones, a minutos del Aeropuerto y con rápido acceso a servicios y locomoción. Alquiler mensual: $15.900 Gastos comunes: $1.500Una opción accesible, cómoda y segura para vivir.Sincronizada desde Casasweb.com ref: CW250513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>190297262</t>
+          <t>193775027</t>
         </is>
       </c>
       <c r="I10" s="2" t="b">
@@ -1263,7 +1276,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
+          <t>https://www.infocasas.com.uy/alquiler-1-dormitorio-en-complejo-cerrado-colonia-nicolich/193775027</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1290,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>15.500</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler 2 dorm. neptunia nte.</t>
+          <t>Casa zona aeropuerto. con alarma incluída y terreno cercado 300m2</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
+          <t>Casa  en Barrio Lacrosse totalmente independiente, cercada, apta para tener mascotas sin que se escapen. Alarma incluida sin costo, puerta blindada, mosquitero en ventanas.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193627120</t>
+          <t>190297262</t>
         </is>
       </c>
       <c r="I11" s="2" t="b">
@@ -1306,7 +1319,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
+          <t>https://www.infocasas.com.uy/casa-zona-aeropuerto-con-alarma-incluida-y-terreno-cercado-300m2/190297262</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1338,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de 1 dormitorio en neptunia</t>
+          <t>Alquiler 2 dorm. neptunia nte.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
+          <t>Alquiler anual, casa en Neptunia norte a media cuadra de   Av. Los Pinos.  2 dormitorios - 2 baños  Cocina - Living comedor  Patio al frente  Patio al fondo  Lugar para auto  $ 15.000 gtía : Aseguradoras  Acepta mascota  El 80% de la casa no tiene cieloraso  Coordine visita  Comisión inm: (mes +iva)    Referencia Interna : Tera-4381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193878393</t>
+          <t>193627120</t>
         </is>
       </c>
       <c r="I12" s="2" t="b">
@@ -1349,7 +1362,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
+          <t>https://www.infocasas.com.uy/alquiler-2-dorm-neptunia-nte/193627120</t>
         </is>
       </c>
     </row>
@@ -1363,27 +1376,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13.500</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa un dormitorio en barros blancos</t>
+          <t>Alquiler casa de 1 dormitorio en neptunia</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Descubra esta encantadora casa de un dormitorio, estratégicamente ubicada sobre la Ruta 10. La propiedad cuenta con un luminoso living, un baño completo y una cocina funcional, complementados por un práctico fondo. Ideal para quienes buscan comodidad y accesibilidad. Se requiere garantía SURA o Santander, con un valor de $15.000.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>194387339</t>
+          <t>193878393</t>
         </is>
       </c>
       <c r="I13" s="2" t="b">
@@ -1392,7 +1405,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-1-dormitorio-en-neptunia/193878393</t>
         </is>
       </c>
     </row>
@@ -1406,27 +1419,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Alquiler casa de un dormitorio en barros blancos</t>
+          <t>Alquiler casa un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Alquiler casa de un dormitorio con patio en Barros Blancos  Se alquila linda casa de un dormitorio con estacionamiento y parrillero en Barros Blancos.  La propiedad se encuentra ubicada sobre Camino al Paso Escobar, a pocas cuadras de Ruta 8 (km 23.500), en una zona de fácil acceso.  Se desarrolla en un padrón amplio que cuenta con tres casas independientes. La unidad en alquiler ofrece total independencia, con entrada propia.  Cuenta con un ambiente amplio y muy luminoso, cocina definida y baño completo de generosas dimensiones. Desde la cocina se accede a un pasillo que conduce a un gran fondo verde con parrillero.  Se trata de una casa totalmente refaccionada, con todas sus aberturas protegidas con rejas.  No dude en coordinar su visita.  Garantía aceptada: aseguradora.  Compartimos con todos los colegas. Comisión inmobiliaria un mes de alquiler mas IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>194409634</t>
+          <t>194387339</t>
         </is>
       </c>
       <c r="I14" s="2" t="b">
@@ -1435,7 +1448,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
+          <t>https://www.infocasas.com.uy/alquiler-casa-un-dormitorio-en-barros-blancos/194387339</t>
         </is>
       </c>
     </row>
@@ -1449,27 +1462,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12.000</t>
+          <t>13.000</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+          <t>Alquiler casa de un dormitorio en barros blancos</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+          <t>Corredor Responsable:  -  Contacto: Sofía  Roytman Hoffmann Se alquila casa de un dormitorio en Barros Blancos.   La propiedad se encuentra ubicada sobre calle Ícaro, a pocas cuadras de Ruta 101, a la altura del km 30.500, en una zona de fácil acceso.  La casa es totalmente independiente y cuenta con ingreso vehicular al frente. Al ingresar, encontramos una amplia cocina-comedor con placares aéreos y bajo mesada, baño completo y un dormitorio de buenas dimensiones.  Desde el dormitorio accedemos al patio del fondo, que cuenta con un alero y parrillero, además de un amplio espacio verde para disfrutar al aire libre.  Garantía: aseguradora.  Compartimos con todos los colegas.  Costo del contrato: un mes de alquiler más IVA. Cada Oficina es de propiedad, gestión y desarrollo independiente La presente publicación describe las características esenciales del inmueble, debiéndose consultar al responsable de la operación por la eventual actualización de las medidas, descripciones arquitectónicas y funcionales, servicios, impuestos, precios y demás información, cuyos valores son aproximados.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>194293172</t>
+          <t>194409634</t>
         </is>
       </c>
       <c r="I15" s="2" t="b">
@@ -1478,12 +1491,55 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
+          <t>https://www.infocasas.com.uy/alquiler-casa-de-un-dormitorio-en-barros-blancos/194409634</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12.000</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Alquiler apartamento un dormitorio en colonia nicolich</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>INMOBILIARIA ALQUILA:  Apartamento ubicado en Colonia Nicolich, calle Torcacitas esquina Camino de los Pinos.  Cercano a Zonamerica, Aeropuerto y rutas 101 y 102.  La unidad se encuentra en Primer piso por escalera.  Cuenta con: Estar comedor Cocina integrada Un dormitorio Baño completo  Posibilidad de entrar un vehículo Predio cerrado con cámaras de seguridad. Más viviendas y oficinas en el predio  Admite mascotas.  ALQUILER: $12.000 GASTOS COMUNES: $500 GARANTIAS: LUC, se evalúa perfil  Comisión inmobiliaria un mes mas IVA que se puede abonar en cuotas, CONSULTE.  Somos Agentes Oficiales de Porto Seguro y Fideciu, no dude tramitar su garantía con nosotros sin compromiso ni costo previo ni adicional.  Consultas y visitas por el 0-9-3- 3-0-4- 9-9-4 whatsapp preferentemente.   *Esta propiedad no admite mascotas.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>194293172</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
           <t>https://www.infocasas.com.uy/alquiler-apartamento-un-dormitorio-en-colonia-nicolich/194293172</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1499,8 +1555,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
 </worksheet>
 </file>